--- a/data/output/espn/merged_formatted.xlsx
+++ b/data/output/espn/merged_formatted.xlsx
@@ -117,6 +117,9 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -124,9 +127,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -884,7 +884,7 @@
       <c r="F12" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="8" t="n">
         <v>36</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -932,7 +932,7 @@
       <c r="B14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C14" s="8" t="n">
+      <c r="C14" s="9" t="n">
         <v>7</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -948,7 +948,7 @@
       <c r="F14" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="G14" s="9" t="n">
         <v>53</v>
       </c>
       <c r="H14" s="3" t="n">
@@ -980,7 +980,7 @@
       <c r="F15" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="9" t="n">
         <v>48</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1044,7 +1044,7 @@
       <c r="F17" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="9" t="n">
         <v>45</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1124,7 +1124,7 @@
       <c r="B20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="7" t="n">
         <v>17</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -1156,7 +1156,7 @@
       <c r="B21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="9" t="n">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -1284,7 +1284,7 @@
       <c r="B25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C25" s="4" t="n">
         <v>18</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1300,7 +1300,7 @@
       <c r="F25" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="G25" s="8" t="n">
+      <c r="G25" s="9" t="n">
         <v>37</v>
       </c>
       <c r="H25" s="3" t="n">
@@ -1404,7 +1404,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -1436,7 +1436,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -1444,7 +1444,7 @@
       <c r="B30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C30" s="8" t="n">
+      <c r="C30" s="9" t="n">
         <v>24</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -1500,7 +1500,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -1540,7 +1540,7 @@
       <c r="B33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="C33" s="6" t="n">
+      <c r="C33" s="4" t="n">
         <v>44</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -1604,7 +1604,7 @@
       <c r="B35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="C35" s="4" t="n">
+      <c r="C35" s="6" t="n">
         <v>38</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -1636,7 +1636,7 @@
       <c r="B36" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="C36" s="4" t="n">
+      <c r="C36" s="6" t="n">
         <v>39</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       <c r="B37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="C37" s="8" t="n">
+      <c r="C37" s="4" t="n">
         <v>28</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -1684,7 +1684,7 @@
       <c r="F37" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="G37" s="8" t="n">
+      <c r="G37" s="9" t="n">
         <v>29</v>
       </c>
       <c r="H37" s="3" t="n">
@@ -1732,7 +1732,7 @@
       <c r="B39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="C39" s="8" t="n">
+      <c r="C39" s="7" t="n">
         <v>29</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -1748,7 +1748,7 @@
       <c r="F39" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="G39" s="8" t="n">
+      <c r="G39" s="4" t="n">
         <v>28</v>
       </c>
       <c r="H39" s="3" t="n">
@@ -1756,7 +1756,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -1764,7 +1764,7 @@
       <c r="B40" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="C40" s="11" t="n">
+      <c r="C40" s="8" t="n">
         <v>57</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -1780,7 +1780,7 @@
       <c r="F40" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="G40" s="8" t="n">
         <v>9</v>
       </c>
       <c r="H40" s="3" t="n">
@@ -1788,7 +1788,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -1796,7 +1796,7 @@
       <c r="B41" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="C41" s="8" t="n">
+      <c r="C41" s="9" t="n">
         <v>33</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -1844,7 +1844,7 @@
       <c r="F42" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="6" t="n">
         <v>15</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -1876,7 +1876,7 @@
       <c r="F43" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="G43" s="6" t="n">
         <v>15</v>
       </c>
       <c r="H43" s="3" t="n">
@@ -1892,7 +1892,7 @@
       <c r="B44" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="C44" s="6" t="n">
+      <c r="C44" s="4" t="n">
         <v>51</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -2020,7 +2020,7 @@
       <c r="B48" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="C48" s="4" t="n">
+      <c r="C48" s="6" t="n">
         <v>54</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -2116,7 +2116,7 @@
       <c r="B51" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="C51" s="11" t="n">
+      <c r="C51" s="8" t="n">
         <v>84</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -2148,7 +2148,7 @@
       <c r="B52" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="C52" s="11" t="n">
+      <c r="C52" s="4" t="n">
         <v>79</v>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -2180,7 +2180,7 @@
       <c r="B53" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="C53" s="4" t="n">
+      <c r="C53" s="6" t="n">
         <v>58</v>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -2340,7 +2340,7 @@
       <c r="B58" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="C58" s="11" t="n">
+      <c r="C58" s="8" t="n">
         <v>74</v>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -2356,7 +2356,7 @@
       <c r="F58" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="G58" s="6" t="n">
         <v>5</v>
       </c>
       <c r="H58" s="3" t="n">
@@ -2372,7 +2372,7 @@
       <c r="B59" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="C59" s="4" t="n">
+      <c r="C59" s="6" t="n">
         <v>63</v>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -2436,7 +2436,7 @@
       <c r="B61" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="C61" s="11" t="n">
+      <c r="C61" s="4" t="n">
         <v>77</v>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -2452,7 +2452,7 @@
       <c r="F61" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="G61" s="6" t="n">
         <v>4</v>
       </c>
       <c r="H61" s="3" t="n">
@@ -2460,7 +2460,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -2492,7 +2492,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -2500,7 +2500,7 @@
       <c r="B63" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="C63" s="11" t="n">
+      <c r="C63" s="8" t="n">
         <v>106</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -2628,7 +2628,7 @@
       <c r="B67" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="C67" s="4" t="n">
+      <c r="C67" s="9" t="n">
         <v>61</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="inlineStr">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -2692,7 +2692,7 @@
       <c r="B69" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="C69" s="11" t="n">
+      <c r="C69" s="4" t="n">
         <v>93</v>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -2788,7 +2788,7 @@
       <c r="B72" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="C72" s="4" t="n">
+      <c r="C72" s="9" t="n">
         <v>67</v>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -2820,7 +2820,7 @@
       <c r="B73" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="C73" s="11" t="n">
+      <c r="C73" s="8" t="n">
         <v>98</v>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -2836,7 +2836,7 @@
       <c r="F73" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="G73" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H73" s="3" t="n">
@@ -2852,7 +2852,7 @@
       <c r="B74" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="C74" s="7" t="n">
+      <c r="C74" s="4" t="n">
         <v>59</v>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -2916,7 +2916,7 @@
       <c r="B76" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="C76" s="11" t="n">
+      <c r="C76" s="8" t="n">
         <v>105</v>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -2948,7 +2948,7 @@
       <c r="B77" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="C77" s="8" t="n">
+      <c r="C77" s="4" t="n">
         <v>64</v>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -3076,7 +3076,7 @@
       <c r="B81" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="C81" s="4" t="n">
+      <c r="C81" s="7" t="n">
         <v>72</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -3108,7 +3108,7 @@
       <c r="B82" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="C82" s="11" t="n">
+      <c r="C82" s="4" t="n">
         <v>109</v>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="9" t="inlineStr">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -3164,7 +3164,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="9" t="inlineStr">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -3172,7 +3172,7 @@
       <c r="B84" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="C84" s="11" t="n">
+      <c r="C84" s="8" t="n">
         <v>127</v>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="9" t="inlineStr">
+      <c r="A85" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -3228,7 +3228,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="9" t="inlineStr">
+      <c r="A86" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -3236,7 +3236,7 @@
       <c r="B86" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="C86" s="11" t="n">
+      <c r="C86" s="4" t="n">
         <v>119</v>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="10" t="inlineStr">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -3292,7 +3292,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="10" t="inlineStr">
+      <c r="A88" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -3324,7 +3324,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="10" t="inlineStr">
+      <c r="A89" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -3396,7 +3396,7 @@
       <c r="B91" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="C91" s="4" t="n">
+      <c r="C91" s="9" t="n">
         <v>87</v>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -3428,7 +3428,7 @@
       <c r="B92" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="C92" s="11" t="n">
+      <c r="C92" s="8" t="n">
         <v>155</v>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -3460,7 +3460,7 @@
       <c r="B93" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="C93" s="11" t="n">
+      <c r="C93" s="4" t="n">
         <v>110</v>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -3620,7 +3620,7 @@
       <c r="B98" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="C98" s="7" t="n">
+      <c r="C98" s="9" t="n">
         <v>70</v>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -3652,7 +3652,7 @@
       <c r="B99" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="C99" s="7" t="n">
+      <c r="C99" s="4" t="n">
         <v>75</v>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -3684,7 +3684,7 @@
       <c r="B100" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="C100" s="4" t="n">
+      <c r="C100" s="8" t="n">
         <v>113</v>
       </c>
       <c r="D100" s="3" t="inlineStr">
@@ -3716,7 +3716,7 @@
       <c r="B101" s="3" t="n">
         <v>101</v>
       </c>
-      <c r="C101" s="8" t="n">
+      <c r="C101" s="4" t="n">
         <v>82</v>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="10" t="inlineStr">
+      <c r="A103" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -3780,7 +3780,7 @@
       <c r="B103" s="3" t="n">
         <v>103</v>
       </c>
-      <c r="C103" s="4" t="n">
+      <c r="C103" s="8" t="n">
         <v>116</v>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="10" t="inlineStr">
+      <c r="A104" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -3836,7 +3836,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="10" t="inlineStr">
+      <c r="A105" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -3868,7 +3868,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="10" t="inlineStr">
+      <c r="A106" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -3940,7 +3940,7 @@
       <c r="B108" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="C108" s="7" t="n">
+      <c r="C108" s="4" t="n">
         <v>83</v>
       </c>
       <c r="D108" s="3" t="inlineStr">
@@ -3972,7 +3972,7 @@
       <c r="B109" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="C109" s="7" t="n">
+      <c r="C109" s="9" t="n">
         <v>81</v>
       </c>
       <c r="D109" s="3" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="9" t="inlineStr">
+      <c r="A113" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -4100,7 +4100,7 @@
       <c r="B113" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="C113" s="4" t="n">
+      <c r="C113" s="7" t="n">
         <v>100</v>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -4132,7 +4132,7 @@
       <c r="B114" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="C114" s="11" t="n">
+      <c r="C114" s="4" t="n">
         <v>163</v>
       </c>
       <c r="D114" s="3" t="inlineStr">
@@ -4196,7 +4196,7 @@
       <c r="B116" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="C116" s="11" t="n">
+      <c r="C116" s="4" t="n">
         <v>150</v>
       </c>
       <c r="D116" s="3" t="inlineStr">
@@ -4228,7 +4228,7 @@
       <c r="B117" s="3" t="n">
         <v>117</v>
       </c>
-      <c r="C117" s="11" t="n">
+      <c r="C117" s="4" t="n">
         <v>153</v>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -4260,7 +4260,7 @@
       <c r="B118" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="C118" s="11" t="n">
+      <c r="C118" s="4" t="n">
         <v>157</v>
       </c>
       <c r="D118" s="3" t="inlineStr">
@@ -4292,7 +4292,7 @@
       <c r="B119" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="C119" s="11" t="n">
+      <c r="C119" s="4" t="n">
         <v>164</v>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="10" t="inlineStr">
+      <c r="A121" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -4380,7 +4380,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="10" t="inlineStr">
+      <c r="A122" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -4412,7 +4412,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="10" t="inlineStr">
+      <c r="A123" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -4444,7 +4444,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="10" t="inlineStr">
+      <c r="A124" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -4476,7 +4476,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="9" t="inlineStr">
+      <c r="A125" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -4484,7 +4484,7 @@
       <c r="B125" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="C125" s="8" t="n">
+      <c r="C125" s="7" t="n">
         <v>101</v>
       </c>
       <c r="D125" s="3" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="9" t="inlineStr">
+      <c r="A126" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -4540,7 +4540,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="9" t="inlineStr">
+      <c r="A127" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -4572,7 +4572,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="9" t="inlineStr">
+      <c r="A128" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -4580,7 +4580,7 @@
       <c r="B128" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="C128" s="4" t="n">
+      <c r="C128" s="9" t="n">
         <v>120</v>
       </c>
       <c r="D128" s="3" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="9" t="inlineStr">
+      <c r="A129" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -4644,7 +4644,7 @@
       <c r="B130" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="C130" s="11" t="n">
+      <c r="C130" s="4" t="n">
         <v>151</v>
       </c>
       <c r="D130" s="3" t="inlineStr">
@@ -4676,7 +4676,7 @@
       <c r="B131" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="C131" s="11" t="n">
+      <c r="C131" s="4" t="n">
         <v>162</v>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -4740,7 +4740,7 @@
       <c r="B133" s="3" t="n">
         <v>133</v>
       </c>
-      <c r="C133" s="4" t="n">
+      <c r="C133" s="7" t="n">
         <v>117</v>
       </c>
       <c r="D133" s="3" t="inlineStr">
@@ -4804,7 +4804,7 @@
       <c r="B135" s="3" t="n">
         <v>135</v>
       </c>
-      <c r="C135" s="11" t="n">
+      <c r="C135" s="4" t="n">
         <v>188</v>
       </c>
       <c r="D135" s="3" t="inlineStr">
@@ -4836,7 +4836,7 @@
       <c r="B136" s="3" t="n">
         <v>136</v>
       </c>
-      <c r="C136" s="11" t="n">
+      <c r="C136" s="8" t="n">
         <v>221</v>
       </c>
       <c r="D136" s="3" t="inlineStr">
@@ -4868,7 +4868,7 @@
       <c r="B137" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="C137" s="11" t="n">
+      <c r="C137" s="8" t="n">
         <v>173</v>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -4964,7 +4964,7 @@
       <c r="B140" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="C140" s="7" t="n">
+      <c r="C140" s="4" t="n">
         <v>111</v>
       </c>
       <c r="D140" s="3" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="9" t="inlineStr">
+      <c r="A141" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -4996,7 +4996,7 @@
       <c r="B141" s="3" t="n">
         <v>141</v>
       </c>
-      <c r="C141" s="11" t="n">
+      <c r="C141" s="4" t="n">
         <v>169</v>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="9" t="inlineStr">
+      <c r="A142" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -5028,7 +5028,7 @@
       <c r="B142" s="3" t="n">
         <v>142</v>
       </c>
-      <c r="C142" s="4" t="n">
+      <c r="C142" s="9" t="n">
         <v>134</v>
       </c>
       <c r="D142" s="3" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="10" t="inlineStr">
+      <c r="A143" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -5084,7 +5084,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="10" t="inlineStr">
+      <c r="A144" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -5092,7 +5092,7 @@
       <c r="B144" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="C144" s="11" t="n">
+      <c r="C144" s="8" t="n">
         <v>176</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="10" t="inlineStr">
+      <c r="A145" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -5156,7 +5156,7 @@
       <c r="B146" s="3" t="n">
         <v>146</v>
       </c>
-      <c r="C146" s="11" t="n">
+      <c r="C146" s="4" t="n">
         <v>165</v>
       </c>
       <c r="D146" s="3" t="inlineStr">
@@ -5220,7 +5220,7 @@
       <c r="B148" s="3" t="n">
         <v>148</v>
       </c>
-      <c r="C148" s="4" t="n">
+      <c r="C148" s="9" t="n">
         <v>142</v>
       </c>
       <c r="D148" s="3" t="inlineStr">
@@ -5252,7 +5252,7 @@
       <c r="B149" s="3" t="n">
         <v>149</v>
       </c>
-      <c r="C149" s="4" t="n">
+      <c r="C149" s="7" t="n">
         <v>135</v>
       </c>
       <c r="D149" s="3" t="inlineStr">
@@ -5284,7 +5284,7 @@
       <c r="B150" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="C150" s="4" t="n">
+      <c r="C150" s="7" t="n">
         <v>137</v>
       </c>
       <c r="D150" s="3" t="inlineStr">
@@ -5316,7 +5316,7 @@
       <c r="B151" s="3" t="n">
         <v>151</v>
       </c>
-      <c r="C151" s="11" t="n">
+      <c r="C151" s="4" t="n">
         <v>195</v>
       </c>
       <c r="D151" s="3" t="inlineStr">
@@ -5348,7 +5348,7 @@
       <c r="B152" s="3" t="n">
         <v>152</v>
       </c>
-      <c r="C152" s="11" t="n">
+      <c r="C152" s="6" t="n">
         <v>218</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
@@ -5380,7 +5380,7 @@
       <c r="B153" s="3" t="n">
         <v>153</v>
       </c>
-      <c r="C153" s="11" t="n">
+      <c r="C153" s="6" t="n">
         <v>184</v>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -5412,7 +5412,7 @@
       <c r="B154" s="3" t="n">
         <v>154</v>
       </c>
-      <c r="C154" s="8" t="n">
+      <c r="C154" s="4" t="n">
         <v>124</v>
       </c>
       <c r="D154" s="3" t="inlineStr">
@@ -5476,7 +5476,7 @@
       <c r="B156" s="3" t="n">
         <v>156</v>
       </c>
-      <c r="C156" s="7" t="n">
+      <c r="C156" s="9" t="n">
         <v>112</v>
       </c>
       <c r="D156" s="3" t="inlineStr">
@@ -5508,7 +5508,7 @@
       <c r="B157" s="3" t="n">
         <v>158</v>
       </c>
-      <c r="C157" s="11" t="n">
+      <c r="C157" s="6" t="n">
         <v>192</v>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -5540,7 +5540,7 @@
       <c r="B158" s="3" t="n">
         <v>159</v>
       </c>
-      <c r="C158" s="11" t="n">
+      <c r="C158" s="6" t="n">
         <v>180</v>
       </c>
       <c r="D158" s="3" t="inlineStr">
@@ -5700,7 +5700,7 @@
       <c r="B163" s="3" t="n">
         <v>164</v>
       </c>
-      <c r="C163" s="11" t="n">
+      <c r="C163" s="6" t="n">
         <v>219</v>
       </c>
       <c r="D163" s="3" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="9" t="inlineStr">
+      <c r="A164" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -5756,7 +5756,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="9" t="inlineStr">
+      <c r="A165" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -5764,7 +5764,7 @@
       <c r="B165" s="3" t="n">
         <v>166</v>
       </c>
-      <c r="C165" s="11" t="n">
+      <c r="C165" s="6" t="n">
         <v>207</v>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="9" t="inlineStr">
+      <c r="A166" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -5820,7 +5820,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="9" t="inlineStr">
+      <c r="A167" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -5988,7 +5988,7 @@
       <c r="B172" s="3" t="n">
         <v>197</v>
       </c>
-      <c r="C172" s="11" t="n">
+      <c r="C172" s="4" t="n">
         <v>223</v>
       </c>
       <c r="D172" s="3" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="10" t="inlineStr">
+      <c r="A173" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -6044,7 +6044,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="10" t="inlineStr">
+      <c r="A174" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -6052,7 +6052,7 @@
       <c r="B174" s="3" t="n">
         <v>199</v>
       </c>
-      <c r="C174" s="8" t="n">
+      <c r="C174" s="9" t="n">
         <v>161</v>
       </c>
       <c r="D174" s="3" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="10" t="inlineStr">
+      <c r="A175" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -6084,7 +6084,7 @@
       <c r="B175" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="C175" s="8" t="n">
+      <c r="C175" s="9" t="n">
         <v>147</v>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -6116,7 +6116,7 @@
       <c r="B176" s="3" t="n">
         <v>201</v>
       </c>
-      <c r="C176" s="8" t="n">
+      <c r="C176" s="9" t="n">
         <v>149</v>
       </c>
       <c r="D176" s="3" t="inlineStr">
@@ -6180,7 +6180,7 @@
       <c r="B178" s="3" t="n">
         <v>203</v>
       </c>
-      <c r="C178" s="8" t="n">
+      <c r="C178" s="9" t="n">
         <v>144</v>
       </c>
       <c r="D178" s="3" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="9" t="inlineStr">
+      <c r="A181" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -6276,7 +6276,7 @@
       <c r="B181" s="3" t="n">
         <v>206</v>
       </c>
-      <c r="C181" s="8" t="n">
+      <c r="C181" s="9" t="n">
         <v>170</v>
       </c>
       <c r="D181" s="3" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="9" t="inlineStr">
+      <c r="A182" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -6340,7 +6340,7 @@
       <c r="B183" s="3" t="n">
         <v>208</v>
       </c>
-      <c r="C183" s="8" t="n">
+      <c r="C183" s="9" t="n">
         <v>140</v>
       </c>
       <c r="D183" s="3" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="9" t="inlineStr">
+      <c r="A190" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -6588,7 +6588,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="9" t="inlineStr">
+      <c r="A191" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -6620,7 +6620,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="9" t="inlineStr">
+      <c r="A192" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -6652,7 +6652,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="10" t="inlineStr">
+      <c r="A193" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -6660,7 +6660,7 @@
       <c r="B193" s="3" t="n">
         <v>218</v>
       </c>
-      <c r="C193" s="8" t="n">
+      <c r="C193" s="9" t="n">
         <v>133</v>
       </c>
       <c r="D193" s="3" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="10" t="inlineStr">
+      <c r="A194" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -6692,7 +6692,7 @@
       <c r="B194" s="3" t="n">
         <v>219</v>
       </c>
-      <c r="C194" s="8" t="n">
+      <c r="C194" s="9" t="n">
         <v>154</v>
       </c>
       <c r="D194" s="3" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="10" t="inlineStr">
+      <c r="A195" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -6724,7 +6724,7 @@
       <c r="B195" s="3" t="n">
         <v>220</v>
       </c>
-      <c r="C195" s="8" t="n">
+      <c r="C195" s="9" t="n">
         <v>175</v>
       </c>
       <c r="D195" s="3" t="inlineStr">
@@ -6788,7 +6788,7 @@
       <c r="B197" s="3" t="n">
         <v>222</v>
       </c>
-      <c r="C197" s="8" t="n">
+      <c r="C197" s="9" t="n">
         <v>152</v>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -6884,7 +6884,7 @@
       <c r="B200" s="3" t="n">
         <v>225</v>
       </c>
-      <c r="C200" s="8" t="n">
+      <c r="C200" s="9" t="n">
         <v>156</v>
       </c>
       <c r="D200" s="3" t="inlineStr">
@@ -6916,7 +6916,7 @@
       <c r="B201" s="3" t="n">
         <v>226</v>
       </c>
-      <c r="C201" s="8" t="n">
+      <c r="C201" s="9" t="n">
         <v>189</v>
       </c>
       <c r="D201" s="3" t="inlineStr">
@@ -6976,7 +6976,7 @@
       <c r="B203" s="3" t="n">
         <v>229</v>
       </c>
-      <c r="C203" s="8" t="n">
+      <c r="C203" s="9" t="n">
         <v>183</v>
       </c>
       <c r="D203" s="3" t="inlineStr">
@@ -7136,7 +7136,7 @@
       <c r="B208" s="3" t="n">
         <v>239</v>
       </c>
-      <c r="C208" s="8" t="n">
+      <c r="C208" s="9" t="n">
         <v>187</v>
       </c>
       <c r="D208" s="3" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="9" t="inlineStr">
+      <c r="A216" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -7416,7 +7416,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="9" t="inlineStr">
+      <c r="A217" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -7448,7 +7448,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="9" t="inlineStr">
+      <c r="A218" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -7488,7 +7488,7 @@
       <c r="B219" s="3" t="n">
         <v>261</v>
       </c>
-      <c r="C219" s="8" t="n">
+      <c r="C219" s="9" t="n">
         <v>191</v>
       </c>
       <c r="D219" s="3" t="inlineStr">
@@ -7648,7 +7648,7 @@
       <c r="B224" s="3" t="n">
         <v>266</v>
       </c>
-      <c r="C224" s="8" t="n">
+      <c r="C224" s="9" t="n">
         <v>177</v>
       </c>
       <c r="D224" s="3" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="10" t="inlineStr">
+      <c r="A225" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -7680,7 +7680,7 @@
       <c r="B225" s="3" t="n">
         <v>267</v>
       </c>
-      <c r="C225" s="8" t="n">
+      <c r="C225" s="9" t="n">
         <v>160</v>
       </c>
       <c r="D225" s="3" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="10" t="inlineStr">
+      <c r="A226" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -7712,7 +7712,7 @@
       <c r="B226" s="3" t="n">
         <v>268</v>
       </c>
-      <c r="C226" s="8" t="n">
+      <c r="C226" s="9" t="n">
         <v>194</v>
       </c>
       <c r="D226" s="3" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="10" t="inlineStr">
+      <c r="A227" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -7744,7 +7744,7 @@
       <c r="B227" s="3" t="n">
         <v>269</v>
       </c>
-      <c r="C227" s="8" t="n">
+      <c r="C227" s="9" t="n">
         <v>186</v>
       </c>
       <c r="D227" s="3" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="10" t="inlineStr">
+      <c r="A228" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -7808,7 +7808,7 @@
       <c r="B229" s="3" t="n">
         <v>271</v>
       </c>
-      <c r="C229" s="8" t="n">
+      <c r="C229" s="9" t="n">
         <v>193</v>
       </c>
       <c r="D229" s="3" t="inlineStr">
@@ -7840,7 +7840,7 @@
       <c r="B230" s="3" t="n">
         <v>272</v>
       </c>
-      <c r="C230" s="8" t="n">
+      <c r="C230" s="9" t="n">
         <v>179</v>
       </c>
       <c r="D230" s="3" t="inlineStr">
@@ -7968,7 +7968,7 @@
       <c r="B234" s="3" t="n">
         <v>283</v>
       </c>
-      <c r="C234" s="8" t="n">
+      <c r="C234" s="9" t="n">
         <v>197</v>
       </c>
       <c r="D234" s="3" t="inlineStr">
@@ -7992,7 +7992,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="9" t="inlineStr">
+      <c r="A235" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -8000,7 +8000,7 @@
       <c r="B235" s="3" t="n">
         <v>289</v>
       </c>
-      <c r="C235" s="8" t="n">
+      <c r="C235" s="9" t="n">
         <v>172</v>
       </c>
       <c r="D235" s="3" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="9" t="inlineStr">
+      <c r="A236" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -8032,7 +8032,7 @@
       <c r="B236" s="3" t="n">
         <v>290</v>
       </c>
-      <c r="C236" s="8" t="n">
+      <c r="C236" s="9" t="n">
         <v>167</v>
       </c>
       <c r="D236" s="3" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="9" t="inlineStr">
+      <c r="A237" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -8064,7 +8064,7 @@
       <c r="B237" s="3" t="n">
         <v>291</v>
       </c>
-      <c r="C237" s="8" t="n">
+      <c r="C237" s="9" t="n">
         <v>199</v>
       </c>
       <c r="D237" s="3" t="inlineStr">
@@ -8088,7 +8088,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="9" t="inlineStr">
+      <c r="A238" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -8120,7 +8120,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="10" t="inlineStr">
+      <c r="A239" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -8128,7 +8128,7 @@
       <c r="B239" s="3" t="n">
         <v>296</v>
       </c>
-      <c r="C239" s="8" t="n">
+      <c r="C239" s="9" t="n">
         <v>185</v>
       </c>
       <c r="D239" s="3" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="10" t="inlineStr">
+      <c r="A240" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -8160,7 +8160,7 @@
       <c r="B240" s="3" t="n">
         <v>301</v>
       </c>
-      <c r="C240" s="8" t="n">
+      <c r="C240" s="9" t="n">
         <v>178</v>
       </c>
       <c r="D240" s="3" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="10" t="inlineStr">
+      <c r="A241" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -8280,7 +8280,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="9" t="inlineStr">
+      <c r="A244" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -8312,7 +8312,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="9" t="inlineStr">
+      <c r="A245" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -8344,7 +8344,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="9" t="inlineStr">
+      <c r="A246" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -8376,7 +8376,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="10" t="inlineStr">
+      <c r="A247" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -8408,7 +8408,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="10" t="inlineStr">
+      <c r="A248" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -8440,7 +8440,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="10" t="inlineStr">
+      <c r="A249" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -8472,7 +8472,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="10" t="inlineStr">
+      <c r="A250" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -8504,7 +8504,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="9" t="inlineStr">
+      <c r="A251" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -8536,7 +8536,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="9" t="inlineStr">
+      <c r="A252" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -8568,7 +8568,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="9" t="inlineStr">
+      <c r="A253" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -8600,7 +8600,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="9" t="inlineStr">
+      <c r="A254" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -8632,7 +8632,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="9" t="inlineStr">
+      <c r="A255" s="10" t="inlineStr">
         <is>
           <t>TE</t>
         </is>

--- a/data/output/espn/merged_formatted.xlsx
+++ b/data/output/espn/merged_formatted.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H262"/>
+  <dimension ref="A1:H269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,7 +613,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
         <v>55</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>4</v>
@@ -728,7 +728,7 @@
         <v>56</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -760,7 +760,7 @@
         <v>53</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -773,7 +773,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>52</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>50</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>10</v>
@@ -868,8 +868,8 @@
       <c r="B12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C12" s="6" t="n">
-        <v>19</v>
+      <c r="C12" s="4" t="n">
+        <v>14</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -884,8 +884,8 @@
       <c r="F12" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="G12" s="8" t="n">
-        <v>36</v>
+      <c r="G12" s="6" t="n">
+        <v>43</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>11</v>
@@ -900,8 +900,8 @@
       <c r="B13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C13" s="4" t="n">
-        <v>14</v>
+      <c r="C13" s="6" t="n">
+        <v>20</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
@@ -916,8 +916,8 @@
       <c r="F13" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="G13" s="4" t="n">
-        <v>43</v>
+      <c r="G13" s="8" t="n">
+        <v>35</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>12</v>
@@ -933,7 +933,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>45</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>13</v>
@@ -1061,7 +1061,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>38</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>17</v>
@@ -1093,7 +1093,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>37</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>18</v>
@@ -1125,7 +1125,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>19</v>
@@ -1156,8 +1156,8 @@
       <c r="B21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C21" s="9" t="n">
-        <v>16</v>
+      <c r="C21" s="4" t="n">
+        <v>22</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>35</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>34</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>21</v>
@@ -1221,7 +1221,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>33</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>22</v>
@@ -1253,7 +1253,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>32</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>24</v>
@@ -1284,8 +1284,8 @@
       <c r="B25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C25" s="4" t="n">
-        <v>18</v>
+      <c r="C25" s="9" t="n">
+        <v>17</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>32</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>23</v>
@@ -1317,7 +1317,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>31</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>25</v>
@@ -1349,7 +1349,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>30</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>26</v>
@@ -1413,7 +1413,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>29</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>28</v>
@@ -1444,8 +1444,8 @@
       <c r="B30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C30" s="9" t="n">
-        <v>24</v>
+      <c r="C30" s="4" t="n">
+        <v>26</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>28</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>29</v>
@@ -1477,7 +1477,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>27</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>30</v>
@@ -1509,7 +1509,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>26</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>31</v>
@@ -1541,7 +1541,7 @@
         <v>32</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>25</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>32</v>
@@ -1573,7 +1573,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>24</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>33</v>
@@ -1604,8 +1604,8 @@
       <c r="B35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="C35" s="6" t="n">
-        <v>38</v>
+      <c r="C35" s="4" t="n">
+        <v>37</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>23</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>34</v>
@@ -1637,7 +1637,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
@@ -1652,11 +1652,11 @@
       <c r="F36" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="G36" s="4" t="n">
-        <v>21</v>
+      <c r="G36" s="6" t="n">
+        <v>15</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37">
@@ -1669,7 +1669,7 @@
         <v>36</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
@@ -1684,11 +1684,11 @@
       <c r="F37" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="G37" s="9" t="n">
-        <v>29</v>
+      <c r="G37" s="4" t="n">
+        <v>22</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38">
@@ -1700,27 +1700,27 @@
       <c r="B38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="C38" s="4" t="n">
-        <v>37</v>
+      <c r="C38" s="7" t="n">
+        <v>29</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Kenneth WalkerI</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
         <v>22</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39">
@@ -1732,27 +1732,27 @@
       <c r="B39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="C39" s="7" t="n">
-        <v>29</v>
+      <c r="C39" s="4" t="n">
+        <v>40</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Kenneth WalkerI</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
         <v>21</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40">
@@ -1765,7 +1765,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="8" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>9</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
@@ -1796,8 +1796,8 @@
       <c r="B41" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="C41" s="9" t="n">
-        <v>33</v>
+      <c r="C41" s="7" t="n">
+        <v>31</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>20</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>40</v>
@@ -1829,7 +1829,7 @@
         <v>41</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
@@ -1844,11 +1844,11 @@
       <c r="F42" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G42" s="6" t="n">
-        <v>15</v>
+      <c r="G42" s="4" t="n">
+        <v>19</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43">
@@ -1861,7 +1861,7 @@
         <v>42</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
@@ -1876,11 +1876,11 @@
       <c r="F43" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G43" s="6" t="n">
-        <v>15</v>
+      <c r="G43" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44">
@@ -1893,7 +1893,7 @@
         <v>43</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
@@ -1908,8 +1908,8 @@
       <c r="F44" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="G44" s="6" t="n">
-        <v>11</v>
+      <c r="G44" s="4" t="n">
+        <v>17</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>43</v>
@@ -1925,23 +1925,23 @@
         <v>44</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G45" s="4" t="n">
-        <v>17</v>
+      <c r="G45" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>44</v>
@@ -1957,7 +1957,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
@@ -1972,8 +1972,8 @@
       <c r="F46" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G46" s="4" t="n">
-        <v>20</v>
+      <c r="G46" s="9" t="n">
+        <v>23</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>45</v>
@@ -1989,7 +1989,7 @@
         <v>46</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
@@ -2005,10 +2005,10 @@
         <v>15</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48">
@@ -2020,27 +2020,27 @@
       <c r="B48" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="C48" s="6" t="n">
-        <v>54</v>
+      <c r="C48" s="4" t="n">
+        <v>39</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Xavier Worthy</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G48" s="6" t="n">
-        <v>10</v>
+      <c r="G48" s="9" t="n">
+        <v>21</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49">
@@ -2050,29 +2050,29 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>52</v>
+        <v>48</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>55</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>10</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50">
@@ -2084,12 +2084,12 @@
       <c r="B50" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="C50" s="7" t="n">
-        <v>32</v>
+      <c r="C50" s="6" t="n">
+        <v>58</v>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Xavier Worthy</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -2100,11 +2100,11 @@
       <c r="F50" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="G50" s="7" t="n">
-        <v>25</v>
+      <c r="G50" s="6" t="n">
+        <v>9</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51">
@@ -2116,24 +2116,24 @@
       <c r="B51" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="C51" s="8" t="n">
-        <v>84</v>
+      <c r="C51" s="4" t="n">
+        <v>53</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Joe Mixon</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G51" s="6" t="n">
-        <v>4</v>
+      <c r="G51" s="4" t="n">
+        <v>10</v>
       </c>
       <c r="H51" s="3" t="n">
         <v>50</v>
@@ -2149,7 +2149,7 @@
         <v>52</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>4</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53">
@@ -2180,8 +2180,8 @@
       <c r="B53" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="C53" s="6" t="n">
-        <v>58</v>
+      <c r="C53" s="4" t="n">
+        <v>56</v>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
@@ -2197,10 +2197,10 @@
         <v>11</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54">
@@ -2213,7 +2213,7 @@
         <v>54</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
@@ -2229,10 +2229,10 @@
         <v>10</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55">
@@ -2261,10 +2261,10 @@
         <v>10</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56">
@@ -2277,7 +2277,7 @@
         <v>56</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>57</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
@@ -2325,10 +2325,10 @@
         <v>10</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58">
@@ -2340,8 +2340,8 @@
       <c r="B58" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="C58" s="8" t="n">
-        <v>74</v>
+      <c r="C58" s="6" t="n">
+        <v>70</v>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
@@ -2356,11 +2356,11 @@
       <c r="F58" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G58" s="6" t="n">
-        <v>5</v>
+      <c r="G58" s="4" t="n">
+        <v>6</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59">
@@ -2373,7 +2373,7 @@
         <v>59</v>
       </c>
       <c r="C59" s="6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>60</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
@@ -2421,10 +2421,10 @@
         <v>9</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="61">
@@ -2437,7 +2437,7 @@
         <v>61</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>4</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="62">
@@ -2468,8 +2468,8 @@
       <c r="B62" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="C62" s="4" t="n">
-        <v>71</v>
+      <c r="C62" s="6" t="n">
+        <v>72</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>6</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63">
@@ -2520,7 +2520,7 @@
         <v>2</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64">
@@ -2552,7 +2552,7 @@
         <v>7</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65">
@@ -2565,7 +2565,7 @@
         <v>65</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
@@ -2581,10 +2581,10 @@
         <v>7</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66">
@@ -2596,8 +2596,8 @@
       <c r="B66" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="C66" s="7" t="n">
-        <v>42</v>
+      <c r="C66" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
@@ -2612,11 +2612,11 @@
       <c r="F66" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G66" s="7" t="n">
-        <v>19</v>
+      <c r="G66" s="4" t="n">
+        <v>12</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67">
@@ -2628,27 +2628,27 @@
       <c r="B67" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="C67" s="9" t="n">
-        <v>61</v>
+      <c r="C67" s="4" t="n">
+        <v>74</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
         <v>7</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="68">
@@ -2661,26 +2661,26 @@
         <v>68</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Aaron Jones</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
         <v>6</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69">
@@ -2693,7 +2693,7 @@
         <v>69</v>
       </c>
       <c r="C69" s="4" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>3</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70">
@@ -2724,27 +2724,27 @@
       <c r="B70" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="C70" s="4" t="n">
-        <v>78</v>
+      <c r="C70" s="7" t="n">
+        <v>61</v>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Aaron Jones</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
         <v>6</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71">
@@ -2757,16 +2757,16 @@
         <v>71</v>
       </c>
       <c r="C71" s="4" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>RJ Harvey</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
@@ -2776,7 +2776,7 @@
         <v>5</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="72">
@@ -2788,24 +2788,24 @@
       <c r="B72" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="C72" s="9" t="n">
-        <v>67</v>
+      <c r="C72" s="4" t="n">
+        <v>73</v>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>RJ Harvey</t>
+          <t>Isiah Pacheco</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
         <v>6</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H72" s="3" t="n">
         <v>69</v>
@@ -2821,7 +2821,7 @@
         <v>73</v>
       </c>
       <c r="C73" s="8" t="n">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
@@ -2836,8 +2836,8 @@
       <c r="F73" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G73" s="6" t="n">
-        <v>2</v>
+      <c r="G73" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="H73" s="3" t="n">
         <v>71</v>
@@ -2853,7 +2853,7 @@
         <v>74</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
@@ -2869,10 +2869,10 @@
         <v>5</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="75">
@@ -2885,7 +2885,7 @@
         <v>75</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>5</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H75" s="3" t="n">
         <v>76</v>
@@ -2916,24 +2916,24 @@
       <c r="B76" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="C76" s="8" t="n">
-        <v>105</v>
+      <c r="C76" s="4" t="n">
+        <v>57</v>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Cooper Kupp</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
         <v>5</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H76" s="3" t="n">
         <v>74</v>
@@ -2948,27 +2948,27 @@
       <c r="B77" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="C77" s="4" t="n">
-        <v>64</v>
+      <c r="C77" s="8" t="n">
+        <v>93</v>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Michael Pittman</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
         <v>5</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="78">
@@ -2980,27 +2980,27 @@
       <c r="B78" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="C78" s="7" t="n">
-        <v>53</v>
+      <c r="C78" s="8" t="n">
+        <v>98</v>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Cooper Kupp</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="79">
@@ -3013,26 +3013,26 @@
         <v>79</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Jordan Addison</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="80">
@@ -3045,26 +3045,26 @@
         <v>80</v>
       </c>
       <c r="C80" s="4" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Kaleb Johnson</t>
+          <t>Tyrone Tracy</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="81">
@@ -3076,27 +3076,27 @@
       <c r="B81" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="C81" s="7" t="n">
-        <v>72</v>
+      <c r="C81" s="4" t="n">
+        <v>109</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Isiah Pacheco</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="82">
@@ -3109,26 +3109,26 @@
         <v>82</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Tyrone Tracy</t>
+          <t>Kaleb Johnson</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="83">
@@ -3140,8 +3140,8 @@
       <c r="B83" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="C83" s="4" t="n">
-        <v>91</v>
+      <c r="C83" s="9" t="n">
+        <v>78</v>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
@@ -3157,10 +3157,10 @@
         <v>4</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="84">
@@ -3173,7 +3173,7 @@
         <v>84</v>
       </c>
       <c r="C84" s="8" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>1</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85">
@@ -3205,7 +3205,7 @@
         <v>85</v>
       </c>
       <c r="C85" s="4" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>3</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86">
@@ -3237,7 +3237,7 @@
         <v>86</v>
       </c>
       <c r="C86" s="4" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>2</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87">
@@ -3269,7 +3269,7 @@
         <v>87</v>
       </c>
       <c r="C87" s="4" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>3</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="88">
@@ -3301,7 +3301,7 @@
         <v>88</v>
       </c>
       <c r="C88" s="4" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>3</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="89">
@@ -3333,7 +3333,7 @@
         <v>89</v>
       </c>
       <c r="C89" s="4" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
@@ -3349,10 +3349,10 @@
         <v>3</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="90">
@@ -3365,23 +3365,23 @@
         <v>90</v>
       </c>
       <c r="C90" s="4" t="n">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Joe Mixon</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H90" s="3" t="n">
         <v>89</v>
@@ -3396,27 +3396,27 @@
       <c r="B91" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="C91" s="9" t="n">
-        <v>87</v>
+      <c r="C91" s="8" t="n">
+        <v>163</v>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Brian Robinson</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="92">
@@ -3428,27 +3428,27 @@
       <c r="B92" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="C92" s="8" t="n">
-        <v>155</v>
+      <c r="C92" s="4" t="n">
+        <v>99</v>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="93">
@@ -3461,7 +3461,7 @@
         <v>93</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>2</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="94">
@@ -3493,26 +3493,26 @@
         <v>94</v>
       </c>
       <c r="C94" s="4" t="n">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F94" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="95">
@@ -3525,26 +3525,26 @@
         <v>95</v>
       </c>
       <c r="C95" s="4" t="n">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Austin Ekeler</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F95" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="96">
@@ -3557,26 +3557,26 @@
         <v>96</v>
       </c>
       <c r="C96" s="4" t="n">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Khalil Shakir</t>
+          <t>Jordan Addison</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="97">
@@ -3588,27 +3588,27 @@
       <c r="B97" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="C97" s="7" t="n">
-        <v>62</v>
+      <c r="C97" s="6" t="n">
+        <v>103</v>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Jauan Jennings</t>
+          <t>Khalil Shakir</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>100</v>
+        <v>119</v>
       </c>
     </row>
     <row r="98">
@@ -3620,27 +3620,27 @@
       <c r="B98" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="C98" s="9" t="n">
-        <v>70</v>
+      <c r="C98" s="7" t="n">
+        <v>49</v>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Deebo Samuel</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="99">
@@ -3652,12 +3652,12 @@
       <c r="B99" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="C99" s="4" t="n">
-        <v>75</v>
+      <c r="C99" s="7" t="n">
+        <v>62</v>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Ricky Pearsall</t>
+          <t>Jauan Jennings</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -3669,10 +3669,10 @@
         <v>2</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="100">
@@ -3684,24 +3684,24 @@
       <c r="B100" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="C100" s="8" t="n">
-        <v>113</v>
+      <c r="C100" s="7" t="n">
+        <v>68</v>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Keon Coleman</t>
+          <t>Deebo Samuel</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H100" s="3" t="n">
         <v>104</v>
@@ -3716,27 +3716,27 @@
       <c r="B101" s="3" t="n">
         <v>101</v>
       </c>
-      <c r="C101" s="4" t="n">
-        <v>82</v>
+      <c r="C101" s="7" t="n">
+        <v>66</v>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Michael Pittman</t>
+          <t>Ricky Pearsall</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F101" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="102">
@@ -3749,16 +3749,16 @@
         <v>102</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Keon Coleman</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F102" s="3" t="n">
@@ -3768,7 +3768,7 @@
         <v>2</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="103">
@@ -3780,8 +3780,8 @@
       <c r="B103" s="3" t="n">
         <v>103</v>
       </c>
-      <c r="C103" s="8" t="n">
-        <v>116</v>
+      <c r="C103" s="4" t="n">
+        <v>111</v>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>2</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="104">
@@ -3813,7 +3813,7 @@
         <v>104</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>2</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="105">
@@ -3845,7 +3845,7 @@
         <v>105</v>
       </c>
       <c r="C105" s="4" t="n">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>2</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="106">
@@ -3877,7 +3877,7 @@
         <v>106</v>
       </c>
       <c r="C106" s="4" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>2</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="107">
@@ -3909,16 +3909,16 @@
         <v>107</v>
       </c>
       <c r="C107" s="4" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Keenan Allen</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F107" s="3" t="n">
@@ -3941,26 +3941,26 @@
         <v>108</v>
       </c>
       <c r="C108" s="4" t="n">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Darnell Mooney</t>
+          <t>Keenan Allen</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F108" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="109">
@@ -3972,17 +3972,17 @@
       <c r="B109" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="C109" s="9" t="n">
-        <v>81</v>
+      <c r="C109" s="4" t="n">
+        <v>82</v>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Josh Downs</t>
+          <t>Darnell Mooney</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F109" s="3" t="n">
@@ -3992,7 +3992,7 @@
         <v>4</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="110">
@@ -4004,27 +4004,27 @@
       <c r="B110" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="C110" s="4" t="n">
-        <v>103</v>
+      <c r="C110" s="9" t="n">
+        <v>81</v>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Rashid Shaheed</t>
+          <t>Josh Downs</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F110" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="111">
@@ -4036,27 +4036,27 @@
       <c r="B111" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="C111" s="4" t="n">
-        <v>104</v>
+      <c r="C111" s="9" t="n">
+        <v>83</v>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Jayden Higgins</t>
+          <t>Rashid Shaheed</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F111" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="112">
@@ -4068,24 +4068,24 @@
       <c r="B112" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="C112" s="7" t="n">
-        <v>69</v>
+      <c r="C112" s="6" t="n">
+        <v>124</v>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Jayden Higgins</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F112" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>97</v>
@@ -4101,26 +4101,26 @@
         <v>113</v>
       </c>
       <c r="C113" s="7" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Tyler Warren</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F113" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="114">
@@ -4132,27 +4132,27 @@
       <c r="B114" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="C114" s="4" t="n">
-        <v>163</v>
+      <c r="C114" s="7" t="n">
+        <v>100</v>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Austin Ekeler</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F114" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="115">
@@ -4165,7 +4165,7 @@
         <v>115</v>
       </c>
       <c r="C115" s="7" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
@@ -4181,10 +4181,10 @@
         <v>2</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="116">
@@ -4197,7 +4197,7 @@
         <v>116</v>
       </c>
       <c r="C116" s="4" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>1</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="117">
@@ -4229,16 +4229,16 @@
         <v>117</v>
       </c>
       <c r="C117" s="4" t="n">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Tank Bigsby</t>
+          <t>Brian Robinson</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F117" s="3" t="n">
@@ -4248,7 +4248,7 @@
         <v>1</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="118">
@@ -4261,16 +4261,16 @@
         <v>118</v>
       </c>
       <c r="C118" s="4" t="n">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Jerome Ford</t>
+          <t>Tank Bigsby</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="F118" s="3" t="n">
@@ -4280,7 +4280,7 @@
         <v>1</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="119">
@@ -4292,27 +4292,27 @@
       <c r="B119" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="C119" s="4" t="n">
-        <v>164</v>
+      <c r="C119" s="7" t="n">
+        <v>102</v>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Rachaad White</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F119" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>95</v>
+        <v>117</v>
       </c>
     </row>
     <row r="120">
@@ -4324,27 +4324,27 @@
       <c r="B120" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="C120" s="7" t="n">
-        <v>88</v>
+      <c r="C120" s="4" t="n">
+        <v>128</v>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F120" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
     </row>
     <row r="121">
@@ -4357,7 +4357,7 @@
         <v>121</v>
       </c>
       <c r="C121" s="4" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
@@ -4373,10 +4373,10 @@
         <v>1</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="122">
@@ -4389,7 +4389,7 @@
         <v>122</v>
       </c>
       <c r="C122" s="4" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>123</v>
       </c>
       <c r="C123" s="4" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
@@ -4437,10 +4437,10 @@
         <v>1</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="124">
@@ -4452,8 +4452,8 @@
       <c r="B124" s="3" t="n">
         <v>124</v>
       </c>
-      <c r="C124" s="4" t="n">
-        <v>132</v>
+      <c r="C124" s="8" t="n">
+        <v>150</v>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>1</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>158</v>
+        <v>125</v>
       </c>
     </row>
     <row r="125">
@@ -4485,7 +4485,7 @@
         <v>125</v>
       </c>
       <c r="C125" s="7" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
@@ -4501,10 +4501,10 @@
         <v>1</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>141</v>
+        <v>156</v>
       </c>
     </row>
     <row r="126">
@@ -4516,27 +4516,27 @@
       <c r="B126" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="C126" s="4" t="n">
-        <v>125</v>
+      <c r="C126" s="7" t="n">
+        <v>90</v>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Dallas Goedert</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F126" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="127">
@@ -4549,16 +4549,16 @@
         <v>127</v>
       </c>
       <c r="C127" s="4" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Jake Ferguson</t>
+          <t>Dallas Goedert</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F127" s="3" t="n">
@@ -4580,17 +4580,17 @@
       <c r="B128" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="C128" s="9" t="n">
-        <v>120</v>
+      <c r="C128" s="4" t="n">
+        <v>136</v>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Dalton Kincaid</t>
+          <t>Jake Ferguson</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F128" s="3" t="n">
@@ -4600,7 +4600,7 @@
         <v>1</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="129">
@@ -4613,16 +4613,16 @@
         <v>129</v>
       </c>
       <c r="C129" s="7" t="n">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Tyler Warren</t>
+          <t>Dalton Kincaid</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F129" s="3" t="n">
@@ -4632,7 +4632,7 @@
         <v>2</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="130">
@@ -4645,26 +4645,26 @@
         <v>130</v>
       </c>
       <c r="C130" s="4" t="n">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Trey Benson</t>
+          <t>Rachaad White</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F130" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="131">
@@ -4677,26 +4677,26 @@
         <v>131</v>
       </c>
       <c r="C131" s="4" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Trey Benson</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F131" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="132">
@@ -4708,27 +4708,27 @@
       <c r="B132" s="3" t="n">
         <v>132</v>
       </c>
-      <c r="C132" s="4" t="n">
-        <v>136</v>
+      <c r="C132" s="7" t="n">
+        <v>95</v>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Dylan Sampson</t>
+          <t>Zach Charbonnet</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F132" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="133">
@@ -4740,27 +4740,27 @@
       <c r="B133" s="3" t="n">
         <v>133</v>
       </c>
-      <c r="C133" s="7" t="n">
-        <v>117</v>
+      <c r="C133" s="4" t="n">
+        <v>196</v>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Zach Charbonnet</t>
+          <t>Jaydon Blue</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F133" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G133" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>157</v>
+        <v>128</v>
       </c>
     </row>
     <row r="134">
@@ -4773,7 +4773,7 @@
         <v>134</v>
       </c>
       <c r="C134" s="4" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>1</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>139</v>
+        <v>154</v>
       </c>
     </row>
     <row r="135">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Jaydon Blue</t>
+          <t>Jaylen Wright</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F135" s="3" t="n">
@@ -4824,7 +4824,7 @@
         <v>0</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>133</v>
+        <v>121</v>
       </c>
     </row>
     <row r="136">
@@ -4837,7 +4837,7 @@
         <v>136</v>
       </c>
       <c r="C136" s="8" t="n">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>0</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="137">
@@ -4868,8 +4868,8 @@
       <c r="B137" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="C137" s="8" t="n">
-        <v>173</v>
+      <c r="C137" s="6" t="n">
+        <v>149</v>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
@@ -4885,10 +4885,10 @@
         <v>1</v>
       </c>
       <c r="G137" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="138">
@@ -4920,7 +4920,7 @@
         <v>1</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="139">
@@ -4932,8 +4932,8 @@
       <c r="B139" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="C139" s="4" t="n">
-        <v>143</v>
+      <c r="C139" s="6" t="n">
+        <v>147</v>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>1</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="140">
@@ -4965,7 +4965,7 @@
         <v>140</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
@@ -4981,10 +4981,10 @@
         <v>1</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="141">
@@ -4997,7 +4997,7 @@
         <v>141</v>
       </c>
       <c r="C141" s="4" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>0</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
     </row>
     <row r="142">
@@ -5028,8 +5028,8 @@
       <c r="B142" s="3" t="n">
         <v>142</v>
       </c>
-      <c r="C142" s="9" t="n">
-        <v>134</v>
+      <c r="C142" s="4" t="n">
+        <v>144</v>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>1</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>154</v>
+        <v>138</v>
       </c>
     </row>
     <row r="143">
@@ -5061,7 +5061,7 @@
         <v>143</v>
       </c>
       <c r="C143" s="4" t="n">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
@@ -5077,10 +5077,10 @@
         <v>1</v>
       </c>
       <c r="G143" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="144">
@@ -5093,7 +5093,7 @@
         <v>144</v>
       </c>
       <c r="C144" s="8" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>0</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="145">
@@ -5125,7 +5125,7 @@
         <v>145</v>
       </c>
       <c r="C145" s="4" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>1</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="146">
@@ -5156,27 +5156,27 @@
       <c r="B146" s="3" t="n">
         <v>146</v>
       </c>
-      <c r="C146" s="4" t="n">
-        <v>165</v>
+      <c r="C146" s="7" t="n">
+        <v>126</v>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Najee Harris</t>
+          <t>Braelon Allen</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F146" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="147">
@@ -5189,26 +5189,26 @@
         <v>147</v>
       </c>
       <c r="C147" s="4" t="n">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Jaylen Wright</t>
+          <t>Jerome Ford</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F147" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="148">
@@ -5220,27 +5220,27 @@
       <c r="B148" s="3" t="n">
         <v>148</v>
       </c>
-      <c r="C148" s="9" t="n">
-        <v>142</v>
+      <c r="C148" s="4" t="n">
+        <v>159</v>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>Najee Harris</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F148" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G148" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="149">
@@ -5253,16 +5253,16 @@
         <v>149</v>
       </c>
       <c r="C149" s="7" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Braelon Allen</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="F149" s="3" t="n">
@@ -5272,7 +5272,7 @@
         <v>1</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="150">
@@ -5284,8 +5284,8 @@
       <c r="B150" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="C150" s="7" t="n">
-        <v>137</v>
+      <c r="C150" s="4" t="n">
+        <v>193</v>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
@@ -5301,10 +5301,10 @@
         <v>1</v>
       </c>
       <c r="G150" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>155</v>
+        <v>120</v>
       </c>
     </row>
     <row r="151">
@@ -5316,27 +5316,27 @@
       <c r="B151" s="3" t="n">
         <v>151</v>
       </c>
-      <c r="C151" s="4" t="n">
-        <v>195</v>
+      <c r="C151" s="7" t="n">
+        <v>127</v>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Ray Davis</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F151" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G151" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
     </row>
     <row r="152">
@@ -5349,16 +5349,16 @@
         <v>152</v>
       </c>
       <c r="C152" s="6" t="n">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Jack Bech</t>
+          <t>Wan'Dale Robinson</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F152" s="3" t="n">
@@ -5368,7 +5368,7 @@
         <v>0</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>137</v>
+        <v>123</v>
       </c>
     </row>
     <row r="153">
@@ -5380,27 +5380,27 @@
       <c r="B153" s="3" t="n">
         <v>153</v>
       </c>
-      <c r="C153" s="6" t="n">
-        <v>184</v>
+      <c r="C153" s="4" t="n">
+        <v>119</v>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson</t>
+          <t>Marvin Mims</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F153" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G153" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="154">
@@ -5413,16 +5413,16 @@
         <v>154</v>
       </c>
       <c r="C154" s="4" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Marvin Mims</t>
+          <t>Christian Kirk</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F154" s="3" t="n">
@@ -5432,7 +5432,7 @@
         <v>1</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="155">
@@ -5445,26 +5445,26 @@
         <v>155</v>
       </c>
       <c r="C155" s="4" t="n">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Kyle Williams</t>
+          <t>Rashod Bateman</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F155" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G155" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="156">
@@ -5476,27 +5476,27 @@
       <c r="B156" s="3" t="n">
         <v>156</v>
       </c>
-      <c r="C156" s="9" t="n">
-        <v>112</v>
+      <c r="C156" s="6" t="n">
+        <v>165</v>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Rashod Bateman</t>
+          <t>Demario Douglas</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F156" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="157">
@@ -5506,19 +5506,19 @@
         </is>
       </c>
       <c r="B157" s="3" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C157" s="6" t="n">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Jalen McMillan</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F157" s="3" t="n">
@@ -5528,39 +5528,39 @@
         <v>0</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>159</v>
-      </c>
-      <c r="C158" s="6" t="n">
-        <v>180</v>
+        <v>160</v>
+      </c>
+      <c r="C158" s="7" t="n">
+        <v>139</v>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Tre Harris</t>
+          <t>Will Shipley</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F158" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G158" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>131</v>
+        <v>155</v>
       </c>
     </row>
     <row r="159">
@@ -5570,29 +5570,29 @@
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="C159" s="7" t="n">
-        <v>118</v>
+        <v>161</v>
+      </c>
+      <c r="C159" s="4" t="n">
+        <v>158</v>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Ray Davis</t>
+          <t>Nick Chubb</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F159" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G159" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>142</v>
+        <v>231</v>
       </c>
     </row>
     <row r="160">
@@ -5602,19 +5602,19 @@
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>161</v>
-      </c>
-      <c r="C160" s="4" t="n">
-        <v>166</v>
+        <v>162</v>
+      </c>
+      <c r="C160" s="6" t="n">
+        <v>226</v>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Roschon Johnson</t>
+          <t>Justice Hill</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F160" s="3" t="n">
@@ -5624,39 +5624,39 @@
         <v>0</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>220</v>
+        <v>178</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="5" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>162</v>
-      </c>
-      <c r="C161" s="4" t="n">
-        <v>139</v>
+        <v>163</v>
+      </c>
+      <c r="C161" s="6" t="n">
+        <v>240</v>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Will Shipley</t>
+          <t>Jack Bech</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F161" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G161" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>232</v>
+        <v>160</v>
       </c>
     </row>
     <row r="162">
@@ -5666,19 +5666,19 @@
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C162" s="4" t="n">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Kyle Williams</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F162" s="3" t="n">
@@ -5688,39 +5688,39 @@
         <v>0</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A163" s="10" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B163" s="3" t="n">
-        <v>164</v>
-      </c>
-      <c r="C163" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="C163" s="4" t="n">
+        <v>177</v>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>Zach Ertz</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" s="3" t="n">
         <v>219</v>
-      </c>
-      <c r="D163" s="3" t="inlineStr">
-        <is>
-          <t>Pat Bryant</t>
-        </is>
-      </c>
-      <c r="E163" s="3" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="F163" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G163" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H163" s="3" t="n">
-        <v>180</v>
       </c>
     </row>
     <row r="164">
@@ -5730,19 +5730,19 @@
         </is>
       </c>
       <c r="B164" s="3" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C164" s="4" t="n">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Chig Okonkwo</t>
+          <t>Jonnu Smith</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F164" s="3" t="n">
@@ -5762,10 +5762,10 @@
         </is>
       </c>
       <c r="B165" s="3" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C165" s="6" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>0</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>240</v>
+        <v>248</v>
       </c>
     </row>
     <row r="166">
@@ -5794,19 +5794,19 @@
         </is>
       </c>
       <c r="B166" s="3" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C166" s="4" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Zach Ertz</t>
+          <t>Brenton Strange</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="F166" s="3" t="n">
@@ -5816,39 +5816,39 @@
         <v>0</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="10" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B167" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="C167" s="4" t="n">
-        <v>168</v>
+        <v>193</v>
+      </c>
+      <c r="C167" s="7" t="n">
+        <v>142</v>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>Jonnu Smith</t>
+          <t>Romeo Doubs</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F167" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G167" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>218</v>
+        <v>251</v>
       </c>
     </row>
     <row r="168">
@@ -5858,46 +5858,46 @@
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>193</v>
-      </c>
-      <c r="C168" s="7" t="n">
-        <v>145</v>
+        <v>194</v>
+      </c>
+      <c r="C168" s="6" t="n">
+        <v>245</v>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>Christian Kirk</t>
+          <t>Tyler Lockett</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F168" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G168" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>229</v>
+        <v>166</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B169" s="3" t="n">
-        <v>194</v>
-      </c>
-      <c r="C169" s="7" t="n">
-        <v>131</v>
+        <v>195</v>
+      </c>
+      <c r="C169" s="4" t="n">
+        <v>222</v>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>Romeo Doubs</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
@@ -5909,10 +5909,10 @@
         <v>0</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>233</v>
+        <v>212</v>
       </c>
     </row>
     <row r="170">
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C170" s="4" t="n">
-        <v>204</v>
+        <v>170</v>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>Justice Hill</t>
+          <t>Roschon Johnson</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F170" s="3" t="n">
@@ -5944,29 +5944,29 @@
         <v>0</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>243</v>
+        <v>225</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="5" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B171" s="3" t="n">
-        <v>196</v>
-      </c>
-      <c r="C171" s="4" t="n">
-        <v>203</v>
+        <v>197</v>
+      </c>
+      <c r="C171" s="6" t="n">
+        <v>269</v>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>Kareem Hunt</t>
+          <t>Nick Westbrook-Ikhine</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F171" s="3" t="n">
@@ -5976,39 +5976,39 @@
         <v>0</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>244</v>
+        <v>194</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A172" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="B172" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="C172" s="4" t="n">
-        <v>223</v>
+        <v>198</v>
+      </c>
+      <c r="C172" s="7" t="n">
+        <v>134</v>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Tyler Lockett</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="F172" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G172" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>159</v>
+        <v>236</v>
       </c>
     </row>
     <row r="173">
@@ -6018,19 +6018,19 @@
         </is>
       </c>
       <c r="B173" s="3" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C173" s="7" t="n">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Cam Ward</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F173" s="3" t="n">
@@ -6040,7 +6040,7 @@
         <v>1</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="174">
@@ -6050,51 +6050,51 @@
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C174" s="9" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>Cameron Ward</t>
+          <t>Michael Penix</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F174" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G174" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B175" s="3" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C175" s="9" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Michael Penix</t>
+          <t>Joshua Palmer</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F175" s="3" t="n">
@@ -6104,7 +6104,7 @@
         <v>1</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>228</v>
+        <v>237</v>
       </c>
     </row>
     <row r="176">
@@ -6114,29 +6114,29 @@
         </is>
       </c>
       <c r="B176" s="3" t="n">
-        <v>201</v>
-      </c>
-      <c r="C176" s="9" t="n">
-        <v>149</v>
+        <v>202</v>
+      </c>
+      <c r="C176" s="6" t="n">
+        <v>278</v>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Demario Douglas</t>
+          <t>Diontae Johnson</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F176" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G176" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>227</v>
+        <v>186</v>
       </c>
     </row>
     <row r="177">
@@ -6146,19 +6146,19 @@
         </is>
       </c>
       <c r="B177" s="3" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C177" s="6" t="n">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Nick Westbrook-Ikhine</t>
+          <t>Brandin Cooks</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F177" s="3" t="n">
@@ -6168,7 +6168,7 @@
         <v>0</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>197</v>
+        <v>185</v>
       </c>
     </row>
     <row r="178">
@@ -6178,19 +6178,19 @@
         </is>
       </c>
       <c r="B178" s="3" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C178" s="9" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>Joshua Palmer</t>
+          <t>Darius Slayton</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F178" s="3" t="n">
@@ -6200,7 +6200,7 @@
         <v>1</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>230</v>
+        <v>239</v>
       </c>
     </row>
     <row r="179">
@@ -6210,19 +6210,19 @@
         </is>
       </c>
       <c r="B179" s="3" t="n">
-        <v>204</v>
-      </c>
-      <c r="C179" s="6" t="n">
-        <v>248</v>
+        <v>205</v>
+      </c>
+      <c r="C179" s="4" t="n">
+        <v>197</v>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>Diontae Johnson</t>
+          <t>DeAndre Hopkins</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F179" s="3" t="n">
@@ -6232,29 +6232,29 @@
         <v>0</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>199</v>
+        <v>260</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A180" s="10" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B180" s="3" t="n">
-        <v>205</v>
-      </c>
-      <c r="C180" s="6" t="n">
-        <v>265</v>
+        <v>206</v>
+      </c>
+      <c r="C180" s="9" t="n">
+        <v>174</v>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>Brandin Cooks</t>
+          <t>Cade Otton</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F180" s="3" t="n">
@@ -6264,7 +6264,7 @@
         <v>0</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>204</v>
+        <v>222</v>
       </c>
     </row>
     <row r="181">
@@ -6274,51 +6274,51 @@
         </is>
       </c>
       <c r="B181" s="3" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C181" s="9" t="n">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>Brenton Strange</t>
+          <t>Chig Okonkwo</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F181" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G181" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>217</v>
+        <v>238</v>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="10" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B182" s="3" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C182" s="4" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>Mason Taylor</t>
+          <t>Pat Bryant</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F182" s="3" t="n">
@@ -6328,7 +6328,7 @@
         <v>0</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>238</v>
+        <v>254</v>
       </c>
     </row>
     <row r="183">
@@ -6338,29 +6338,29 @@
         </is>
       </c>
       <c r="B183" s="3" t="n">
-        <v>208</v>
-      </c>
-      <c r="C183" s="9" t="n">
-        <v>140</v>
+        <v>209</v>
+      </c>
+      <c r="C183" s="4" t="n">
+        <v>184</v>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>Darius Slayton</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F183" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G183" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="184">
@@ -6370,19 +6370,19 @@
         </is>
       </c>
       <c r="B184" s="3" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C184" s="4" t="n">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>DeAndre Hopkins</t>
+          <t>Dont'e Thornton</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F184" s="3" t="n">
@@ -6392,7 +6392,7 @@
         <v>0</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="185">
@@ -6402,19 +6402,19 @@
         </is>
       </c>
       <c r="B185" s="3" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C185" s="4" t="n">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Adonai Mitchell</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F185" s="3" t="n">
@@ -6424,39 +6424,39 @@
         <v>0</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>237</v>
+        <v>214</v>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B186" s="3" t="n">
-        <v>211</v>
-      </c>
-      <c r="C186" s="4" t="n">
-        <v>225</v>
+        <v>212</v>
+      </c>
+      <c r="C186" s="7" t="n">
+        <v>101</v>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Dont'e Thornton</t>
+          <t>Dylan Sampson</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F186" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G186" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>175</v>
+        <v>263</v>
       </c>
     </row>
     <row r="187">
@@ -6466,19 +6466,19 @@
         </is>
       </c>
       <c r="B187" s="3" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C187" s="4" t="n">
-        <v>190</v>
+        <v>223</v>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F187" s="3" t="n">
@@ -6488,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>255</v>
+        <v>181</v>
       </c>
     </row>
     <row r="188">
@@ -6498,19 +6498,19 @@
         </is>
       </c>
       <c r="B188" s="3" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C188" s="4" t="n">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Nick Chubb</t>
+          <t>Kareem Hunt</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F188" s="3" t="n">
@@ -6520,29 +6520,29 @@
         <v>0</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>242</v>
+        <v>179</v>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="5" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A189" s="10" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B189" s="3" t="n">
-        <v>214</v>
-      </c>
-      <c r="C189" s="4" t="n">
-        <v>230</v>
+        <v>215</v>
+      </c>
+      <c r="C189" s="9" t="n">
+        <v>162</v>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Mason Taylor</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F189" s="3" t="n">
@@ -6552,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>171</v>
+        <v>229</v>
       </c>
     </row>
     <row r="190">
@@ -6562,19 +6562,19 @@
         </is>
       </c>
       <c r="B190" s="3" t="n">
-        <v>215</v>
-      </c>
-      <c r="C190" s="4" t="n">
-        <v>201</v>
+        <v>216</v>
+      </c>
+      <c r="C190" s="6" t="n">
+        <v>255</v>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Cade Otton</t>
+          <t>Pat Freiermuth</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F190" s="3" t="n">
@@ -6584,7 +6584,7 @@
         <v>0</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>246</v>
+        <v>206</v>
       </c>
     </row>
     <row r="191">
@@ -6594,19 +6594,19 @@
         </is>
       </c>
       <c r="B191" s="3" t="n">
-        <v>216</v>
-      </c>
-      <c r="C191" s="4" t="n">
-        <v>238</v>
+        <v>217</v>
+      </c>
+      <c r="C191" s="9" t="n">
+        <v>175</v>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>Pat Freiermuth</t>
+          <t>Dalton Schultz</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F191" s="3" t="n">
@@ -6616,39 +6616,39 @@
         <v>0</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>179</v>
+        <v>221</v>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="10" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A192" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="B192" s="3" t="n">
-        <v>217</v>
-      </c>
-      <c r="C192" s="4" t="n">
-        <v>202</v>
+        <v>218</v>
+      </c>
+      <c r="C192" s="9" t="n">
+        <v>140</v>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Dalton Schultz</t>
+          <t>Bryce Young</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F192" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G192" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>245</v>
+        <v>168</v>
       </c>
     </row>
     <row r="193">
@@ -6658,19 +6658,19 @@
         </is>
       </c>
       <c r="B193" s="3" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C193" s="9" t="n">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>Bryce Young</t>
+          <t>Geno Smith</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F193" s="3" t="n">
@@ -6680,7 +6680,7 @@
         <v>1</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>209</v>
+        <v>233</v>
       </c>
     </row>
     <row r="194">
@@ -6690,51 +6690,51 @@
         </is>
       </c>
       <c r="B194" s="3" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C194" s="9" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Geno Smith</t>
+          <t>Sam Darnold</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F194" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G194" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A195" s="5" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B195" s="3" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C195" s="9" t="n">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>Anthony Richardson</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="F195" s="3" t="n">
@@ -6744,7 +6744,7 @@
         <v>0</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>213</v>
+        <v>256</v>
       </c>
     </row>
     <row r="196">
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="B196" s="3" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C196" s="4" t="n">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>0</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>251</v>
+        <v>265</v>
       </c>
     </row>
     <row r="197">
@@ -6786,10 +6786,10 @@
         </is>
       </c>
       <c r="B197" s="3" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C197" s="9" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
@@ -6808,61 +6808,57 @@
         <v>1</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>226</v>
+        <v>235</v>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="5" t="inlineStr">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="C198" s="6" t="n">
+        <v>279</v>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>Amari Cooper</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr"/>
+      <c r="F198" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G198" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" s="3" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="5" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="B198" s="3" t="n">
-        <v>223</v>
-      </c>
-      <c r="C198" s="4" t="n">
-        <v>217</v>
-      </c>
-      <c r="D198" s="3" t="inlineStr">
-        <is>
-          <t>Raheem Mostert</t>
-        </is>
-      </c>
-      <c r="E198" s="3" t="inlineStr">
-        <is>
-          <t>LV</t>
-        </is>
-      </c>
-      <c r="F198" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G198" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H198" s="3" t="n">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
       <c r="B199" s="3" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C199" s="4" t="n">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Adonai Mitchell</t>
+          <t>Miles Sanders</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F199" s="3" t="n">
@@ -6872,7 +6868,7 @@
         <v>0</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>164</v>
+        <v>261</v>
       </c>
     </row>
     <row r="200">
@@ -6882,51 +6878,51 @@
         </is>
       </c>
       <c r="B200" s="3" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C200" s="9" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Miles Sanders</t>
+          <t>DJ Giddens</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F200" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G200" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="5" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B201" s="3" t="n">
-        <v>226</v>
-      </c>
-      <c r="C201" s="9" t="n">
-        <v>189</v>
+        <v>228</v>
+      </c>
+      <c r="C201" s="4" t="n">
+        <v>233</v>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Ray-Ray McCloudI</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F201" s="3" t="n">
@@ -6936,7 +6932,7 @@
         <v>0</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>256</v>
+        <v>182</v>
       </c>
     </row>
     <row r="202">
@@ -6946,17 +6942,21 @@
         </is>
       </c>
       <c r="B202" s="3" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C202" s="4" t="n">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>Amari Cooper</t>
-        </is>
-      </c>
-      <c r="E202" s="3" t="inlineStr"/>
+          <t>Josh Reynolds</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>NYJ</t>
+        </is>
+      </c>
       <c r="F202" s="3" t="n">
         <v>0</v>
       </c>
@@ -6964,7 +6964,7 @@
         <v>0</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
     </row>
     <row r="203">
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="B203" s="3" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C203" s="9" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>0</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>260</v>
+        <v>241</v>
       </c>
     </row>
     <row r="204">
@@ -7006,19 +7006,19 @@
         </is>
       </c>
       <c r="B204" s="3" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C204" s="4" t="n">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>Josh Reynolds</t>
+          <t>Tutu Atwell</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="F204" s="3" t="n">
@@ -7028,7 +7028,7 @@
         <v>0</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="205">
@@ -7038,19 +7038,19 @@
         </is>
       </c>
       <c r="B205" s="3" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C205" s="4" t="n">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>Ray-Ray McCloudI</t>
+          <t>Calvin AustinI</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F205" s="3" t="n">
@@ -7060,7 +7060,7 @@
         <v>0</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="206">
@@ -7070,19 +7070,19 @@
         </is>
       </c>
       <c r="B206" s="3" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C206" s="4" t="n">
-        <v>222</v>
+        <v>267</v>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>Tutu Atwell</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F206" s="3" t="n">
@@ -7092,7 +7092,7 @@
         <v>0</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>178</v>
+        <v>196</v>
       </c>
     </row>
     <row r="207">
@@ -7102,19 +7102,19 @@
         </is>
       </c>
       <c r="B207" s="3" t="n">
-        <v>233</v>
-      </c>
-      <c r="C207" s="4" t="n">
-        <v>209</v>
+        <v>234</v>
+      </c>
+      <c r="C207" s="9" t="n">
+        <v>198</v>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>Calvin AustinI</t>
+          <t>Tre Tucker</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F207" s="3" t="n">
@@ -7124,7 +7124,7 @@
         <v>0</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>211</v>
+        <v>259</v>
       </c>
     </row>
     <row r="208">
@@ -7134,19 +7134,19 @@
         </is>
       </c>
       <c r="B208" s="3" t="n">
-        <v>239</v>
-      </c>
-      <c r="C208" s="9" t="n">
-        <v>187</v>
+        <v>242</v>
+      </c>
+      <c r="C208" s="4" t="n">
+        <v>274</v>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>DJ Giddens</t>
+          <t>Elijah Mitchell</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F208" s="3" t="n">
@@ -7156,7 +7156,7 @@
         <v>0</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>257</v>
+        <v>190</v>
       </c>
     </row>
     <row r="209">
@@ -7166,19 +7166,19 @@
         </is>
       </c>
       <c r="B209" s="3" t="n">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C209" s="4" t="n">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>Trevor Etienne</t>
+          <t>Raheem Mostert</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F209" s="3" t="n">
@@ -7188,7 +7188,7 @@
         <v>0</v>
       </c>
       <c r="H209" s="3" t="n">
-        <v>203</v>
+        <v>180</v>
       </c>
     </row>
     <row r="210">
@@ -7198,19 +7198,19 @@
         </is>
       </c>
       <c r="B210" s="3" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C210" s="4" t="n">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>Jarquez Hunter</t>
+          <t>Kyle Monangai</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F210" s="3" t="n">
@@ -7220,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="211">
@@ -7230,19 +7230,19 @@
         </is>
       </c>
       <c r="B211" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="C211" s="4" t="n">
-        <v>261</v>
+        <v>246</v>
+      </c>
+      <c r="C211" s="9" t="n">
+        <v>187</v>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>Jaleel McLaughlin</t>
+          <t>Ollie Gordon</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F211" s="3" t="n">
@@ -7252,7 +7252,7 @@
         <v>0</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>186</v>
+        <v>267</v>
       </c>
     </row>
     <row r="212">
@@ -7262,19 +7262,19 @@
         </is>
       </c>
       <c r="B212" s="3" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C212" s="4" t="n">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>Devin Singletary</t>
+          <t>Sean Tucker</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F212" s="3" t="n">
@@ -7284,7 +7284,7 @@
         <v>0</v>
       </c>
       <c r="H212" s="3" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="213">
@@ -7297,16 +7297,16 @@
         <v>248</v>
       </c>
       <c r="C213" s="4" t="n">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>Elijah Mitchell</t>
+          <t>Isaiah Davis</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F213" s="3" t="n">
@@ -7316,7 +7316,7 @@
         <v>0</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="214">
@@ -7326,19 +7326,19 @@
         </is>
       </c>
       <c r="B214" s="3" t="n">
-        <v>251</v>
-      </c>
-      <c r="C214" s="4" t="n">
-        <v>259</v>
+        <v>249</v>
+      </c>
+      <c r="C214" s="9" t="n">
+        <v>190</v>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>Ollie Gordon</t>
+          <t>Keaton Mitchell</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F214" s="3" t="n">
@@ -7348,95 +7348,95 @@
         <v>0</v>
       </c>
       <c r="H214" s="3" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="5" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="C215" s="4" t="n">
+        <v>276</v>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>Devin Neal</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F215" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G215" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" s="3" t="n">
         <v>188</v>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B215" s="3" t="n">
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="n">
+        <v>252</v>
+      </c>
+      <c r="C216" s="4" t="n">
+        <v>260</v>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>Noah Brown</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" s="3" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="n">
         <v>253</v>
       </c>
-      <c r="C215" s="4" t="n">
-        <v>266</v>
-      </c>
-      <c r="D215" s="3" t="inlineStr">
+      <c r="C217" s="4" t="n">
+        <v>265</v>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
         <is>
           <t>Allen Lazard</t>
         </is>
       </c>
-      <c r="E215" s="3" t="inlineStr">
+      <c r="E217" s="3" t="inlineStr">
         <is>
           <t>NYJ</t>
         </is>
       </c>
-      <c r="F215" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G215" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H215" s="3" t="n">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="10" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B216" s="3" t="n">
-        <v>258</v>
-      </c>
-      <c r="C216" s="4" t="n">
-        <v>231</v>
-      </c>
-      <c r="D216" s="3" t="inlineStr">
-        <is>
-          <t>Elijah Arroyo</t>
-        </is>
-      </c>
-      <c r="E216" s="3" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="F216" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G216" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H216" s="3" t="n">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="10" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B217" s="3" t="n">
-        <v>259</v>
-      </c>
-      <c r="C217" s="4" t="n">
-        <v>208</v>
-      </c>
-      <c r="D217" s="3" t="inlineStr">
-        <is>
-          <t>Mike Gesicki</t>
-        </is>
-      </c>
-      <c r="E217" s="3" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
       <c r="F217" s="3" t="n">
         <v>0</v>
       </c>
@@ -7444,7 +7444,7 @@
         <v>0</v>
       </c>
       <c r="H217" s="3" t="n">
-        <v>239</v>
+        <v>197</v>
       </c>
     </row>
     <row r="218">
@@ -7454,85 +7454,85 @@
         </is>
       </c>
       <c r="B218" s="3" t="n">
+        <v>258</v>
+      </c>
+      <c r="C218" s="4" t="n">
+        <v>252</v>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>Elijah Arroyo</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" s="3" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="10" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="n">
+        <v>259</v>
+      </c>
+      <c r="C219" s="4" t="n">
+        <v>209</v>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>Mike Gesicki</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" s="3" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="10" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="C218" s="4" t="n">
-        <v>237</v>
-      </c>
-      <c r="D218" s="3" t="inlineStr">
+      <c r="C220" s="4" t="n">
+        <v>254</v>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
         <is>
           <t>Tyler Higbee</t>
         </is>
       </c>
-      <c r="E218" s="3" t="inlineStr">
+      <c r="E220" s="3" t="inlineStr">
         <is>
           <t>LA</t>
         </is>
       </c>
-      <c r="F218" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G218" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H218" s="3" t="n">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B219" s="3" t="n">
-        <v>261</v>
-      </c>
-      <c r="C219" s="9" t="n">
-        <v>191</v>
-      </c>
-      <c r="D219" s="3" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
-      <c r="E219" s="3" t="inlineStr">
-        <is>
-          <t>IND</t>
-        </is>
-      </c>
-      <c r="F219" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G219" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H219" s="3" t="n">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B220" s="3" t="n">
-        <v>262</v>
-      </c>
-      <c r="C220" s="4" t="n">
-        <v>224</v>
-      </c>
-      <c r="D220" s="3" t="inlineStr">
-        <is>
-          <t>KaVontae Turpin</t>
-        </is>
-      </c>
-      <c r="E220" s="3" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
       <c r="F220" s="3" t="n">
         <v>0</v>
       </c>
@@ -7540,7 +7540,7 @@
         <v>0</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="221">
@@ -7550,19 +7550,19 @@
         </is>
       </c>
       <c r="B221" s="3" t="n">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C221" s="4" t="n">
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>Andrei Iosivas</t>
+          <t>KaVontae Turpin</t>
         </is>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F221" s="3" t="n">
@@ -7572,7 +7572,7 @@
         <v>0</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>173</v>
+        <v>199</v>
       </c>
     </row>
     <row r="222">
@@ -7582,10 +7582,10 @@
         </is>
       </c>
       <c r="B222" s="3" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C222" s="4" t="n">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
@@ -7608,89 +7608,89 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="5" t="inlineStr">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="n">
+        <v>263</v>
+      </c>
+      <c r="C223" s="4" t="n">
+        <v>217</v>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>Andrei Iosivas</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" s="3" t="n">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="C224" s="4" t="n">
+        <v>249</v>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>Jalen McMillan</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" s="3" t="n">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="B223" s="3" t="n">
-        <v>265</v>
-      </c>
-      <c r="C223" s="4" t="n">
-        <v>213</v>
-      </c>
-      <c r="D223" s="3" t="inlineStr">
-        <is>
-          <t>Sean Tucker</t>
-        </is>
-      </c>
-      <c r="E223" s="3" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="F223" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G223" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H223" s="3" t="n">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="5" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B224" s="3" t="n">
+      <c r="B225" s="3" t="n">
         <v>266</v>
       </c>
-      <c r="C224" s="9" t="n">
-        <v>177</v>
-      </c>
-      <c r="D224" s="3" t="inlineStr">
-        <is>
-          <t>Keaton Mitchell</t>
-        </is>
-      </c>
-      <c r="E224" s="3" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="F224" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G224" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H224" s="3" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B225" s="3" t="n">
-        <v>267</v>
-      </c>
-      <c r="C225" s="9" t="n">
-        <v>160</v>
+      <c r="C225" s="4" t="n">
+        <v>221</v>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>Sam Darnold</t>
+          <t>Jarquez Hunter</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="F225" s="3" t="n">
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>222</v>
+        <v>207</v>
       </c>
     </row>
     <row r="226">
@@ -7710,19 +7710,19 @@
         </is>
       </c>
       <c r="B226" s="3" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C226" s="9" t="n">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>Aaron Rodgers</t>
+          <t>Daniel Jones</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F226" s="3" t="n">
@@ -7732,7 +7732,7 @@
         <v>0</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>252</v>
+        <v>218</v>
       </c>
     </row>
     <row r="227">
@@ -7742,19 +7742,19 @@
         </is>
       </c>
       <c r="B227" s="3" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C227" s="9" t="n">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>Russell Wilson</t>
+          <t>Aaron Rodgers</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F227" s="3" t="n">
@@ -7764,7 +7764,7 @@
         <v>0</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>258</v>
+        <v>216</v>
       </c>
     </row>
     <row r="228">
@@ -7774,51 +7774,51 @@
         </is>
       </c>
       <c r="B228" s="3" t="n">
+        <v>269</v>
+      </c>
+      <c r="C228" s="4" t="n">
+        <v>207</v>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>Russell Wilson</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>NYG</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" s="3" t="n">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="n">
         <v>270</v>
       </c>
-      <c r="C228" s="4" t="n">
-        <v>240</v>
-      </c>
-      <c r="D228" s="3" t="inlineStr">
-        <is>
-          <t>Tyler Shough</t>
-        </is>
-      </c>
-      <c r="E228" s="3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F228" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G228" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H228" s="3" t="n">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B229" s="3" t="n">
-        <v>271</v>
-      </c>
-      <c r="C229" s="9" t="n">
-        <v>193</v>
+      <c r="C229" s="4" t="n">
+        <v>213</v>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>Jaylin Noel</t>
+          <t>Joe Flacco</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F229" s="3" t="n">
@@ -7828,7 +7828,7 @@
         <v>0</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
     <row r="230">
@@ -7838,19 +7838,19 @@
         </is>
       </c>
       <c r="B230" s="3" t="n">
-        <v>272</v>
-      </c>
-      <c r="C230" s="9" t="n">
-        <v>179</v>
+        <v>271</v>
+      </c>
+      <c r="C230" s="4" t="n">
+        <v>201</v>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>Jalen Coker</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F230" s="3" t="n">
@@ -7860,7 +7860,7 @@
         <v>0</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>236</v>
+        <v>255</v>
       </c>
     </row>
     <row r="231">
@@ -7872,17 +7872,17 @@
       <c r="B231" s="3" t="n">
         <v>273</v>
       </c>
-      <c r="C231" s="4" t="n">
-        <v>210</v>
+      <c r="C231" s="9" t="n">
+        <v>183</v>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>Tre Tucker</t>
+          <t>Jalen Coker</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F231" s="3" t="n">
@@ -7892,7 +7892,7 @@
         <v>0</v>
       </c>
       <c r="H231" s="3" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
     </row>
     <row r="232">
@@ -7902,19 +7902,19 @@
         </is>
       </c>
       <c r="B232" s="3" t="n">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C232" s="4" t="n">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>Devin Neal</t>
+          <t>Trevor Etienne</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F232" s="3" t="n">
@@ -7924,7 +7924,7 @@
         <v>0</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>261</v>
+        <v>171</v>
       </c>
     </row>
     <row r="233">
@@ -7934,19 +7934,19 @@
         </is>
       </c>
       <c r="B233" s="3" t="n">
-        <v>279</v>
-      </c>
-      <c r="C233" s="4" t="n">
-        <v>206</v>
+        <v>282</v>
+      </c>
+      <c r="C233" s="9" t="n">
+        <v>192</v>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>Kyle Monangai</t>
+          <t>Tahj Brooks</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F233" s="3" t="n">
@@ -7956,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>241</v>
+        <v>264</v>
       </c>
     </row>
     <row r="234">
@@ -7968,17 +7968,17 @@
       <c r="B234" s="3" t="n">
         <v>283</v>
       </c>
-      <c r="C234" s="9" t="n">
-        <v>197</v>
+      <c r="C234" s="4" t="n">
+        <v>230</v>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>Tahj Brooks</t>
+          <t>Brashard Smith</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F234" s="3" t="n">
@@ -7988,7 +7988,7 @@
         <v>0</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>249</v>
+        <v>174</v>
       </c>
     </row>
     <row r="235">
@@ -8001,7 +8001,7 @@
         <v>289</v>
       </c>
       <c r="C235" s="9" t="n">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>290</v>
       </c>
       <c r="C236" s="9" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>0</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="237">
@@ -8064,8 +8064,8 @@
       <c r="B237" s="3" t="n">
         <v>291</v>
       </c>
-      <c r="C237" s="9" t="n">
-        <v>199</v>
+      <c r="C237" s="4" t="n">
+        <v>210</v>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>0</v>
       </c>
       <c r="H237" s="3" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="238">
@@ -8097,7 +8097,7 @@
         <v>292</v>
       </c>
       <c r="C238" s="4" t="n">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
@@ -8116,29 +8116,29 @@
         <v>0</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>247</v>
+        <v>213</v>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B239" s="3" t="n">
-        <v>296</v>
-      </c>
-      <c r="C239" s="9" t="n">
-        <v>185</v>
+        <v>294</v>
+      </c>
+      <c r="C239" s="4" t="n">
+        <v>235</v>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>Daniel Jones</t>
+          <t>Jalen Nailor</t>
         </is>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F239" s="3" t="n">
@@ -8148,29 +8148,29 @@
         <v>0</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>259</v>
+        <v>169</v>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B240" s="3" t="n">
-        <v>301</v>
-      </c>
-      <c r="C240" s="9" t="n">
-        <v>178</v>
+        <v>295</v>
+      </c>
+      <c r="C240" s="4" t="n">
+        <v>234</v>
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Devaughn Vele</t>
         </is>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F240" s="3" t="n">
@@ -8180,7 +8180,7 @@
         <v>0</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>235</v>
+        <v>170</v>
       </c>
     </row>
     <row r="241">
@@ -8190,147 +8190,147 @@
         </is>
       </c>
       <c r="B241" s="3" t="n">
+        <v>296</v>
+      </c>
+      <c r="C241" s="4" t="n">
+        <v>232</v>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>Tyler Shough</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" s="3" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="C242" s="9" t="n">
+        <v>180</v>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>NYG</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G242" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H242" s="3" t="n">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="n">
         <v>302</v>
       </c>
-      <c r="C241" s="4" t="n">
-        <v>241</v>
-      </c>
-      <c r="D241" s="3" t="inlineStr">
-        <is>
-          <t>Kenny Pickett</t>
-        </is>
-      </c>
-      <c r="E241" s="3" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="F241" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G241" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H241" s="3" t="n">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="5" t="inlineStr">
+      <c r="C243" s="4" t="n">
+        <v>214</v>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>Anthony Richardson</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G243" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" s="3" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="5" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="B242" s="3" t="n">
-        <v>303</v>
-      </c>
-      <c r="C242" s="4" t="n">
-        <v>245</v>
-      </c>
-      <c r="D242" s="3" t="inlineStr">
-        <is>
-          <t>Brashard Smith</t>
-        </is>
-      </c>
-      <c r="E242" s="3" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="F242" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G242" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H242" s="3" t="n">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="5" t="inlineStr">
+      <c r="B244" s="3" t="n">
+        <v>304</v>
+      </c>
+      <c r="C244" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>Devin Singletary</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>NYG</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G244" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" s="3" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="5" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="B243" s="3" t="n">
-        <v>304</v>
-      </c>
-      <c r="C243" s="4" t="n">
-        <v>215</v>
-      </c>
-      <c r="D243" s="3" t="inlineStr">
-        <is>
-          <t>Isaiah Davis</t>
-        </is>
-      </c>
-      <c r="E243" s="3" t="inlineStr">
-        <is>
-          <t>NYJ</t>
-        </is>
-      </c>
-      <c r="F243" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G243" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H243" s="3" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="10" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B244" s="3" t="n">
-        <v>312</v>
-      </c>
-      <c r="C244" s="4" t="n">
-        <v>236</v>
-      </c>
-      <c r="D244" s="3" t="inlineStr">
-        <is>
-          <t>Noah Fant</t>
-        </is>
-      </c>
-      <c r="E244" s="3" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="F244" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G244" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H244" s="3" t="n">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="10" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
       <c r="B245" s="3" t="n">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="C245" s="4" t="n">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>Ben Sinnott</t>
+          <t>Jaleel McLaughlin</t>
         </is>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F245" s="3" t="n">
@@ -8350,115 +8350,115 @@
         </is>
       </c>
       <c r="B246" s="3" t="n">
+        <v>311</v>
+      </c>
+      <c r="C246" s="4" t="n">
+        <v>253</v>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>Noah Fant</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="F246" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G246" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" s="3" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="10" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="n">
+        <v>312</v>
+      </c>
+      <c r="C247" s="4" t="n">
+        <v>272</v>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>Ben Sinnott</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" s="3" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="10" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="n">
+        <v>313</v>
+      </c>
+      <c r="C248" s="4" t="n">
+        <v>251</v>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>Terrance Ferguson</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" s="3" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="10" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="n">
         <v>314</v>
       </c>
-      <c r="C246" s="4" t="n">
-        <v>232</v>
-      </c>
-      <c r="D246" s="3" t="inlineStr">
-        <is>
-          <t>Terrance Ferguson</t>
-        </is>
-      </c>
-      <c r="E246" s="3" t="inlineStr">
-        <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="F246" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G246" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H246" s="3" t="n">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B247" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="C247" s="4" t="n">
-        <v>262</v>
-      </c>
-      <c r="D247" s="3" t="inlineStr">
-        <is>
-          <t>Joe Flacco</t>
-        </is>
-      </c>
-      <c r="E247" s="3" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="F247" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G247" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H247" s="3" t="n">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B248" s="3" t="n">
-        <v>317</v>
-      </c>
-      <c r="C248" s="4" t="n">
-        <v>227</v>
-      </c>
-      <c r="D248" s="3" t="inlineStr">
-        <is>
-          <t>Spencer Rattler</t>
-        </is>
-      </c>
-      <c r="E248" s="3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F248" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G248" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H248" s="3" t="n">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B249" s="3" t="n">
-        <v>318</v>
-      </c>
       <c r="C249" s="4" t="n">
-        <v>242</v>
+        <v>212</v>
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>Kirk Cousins</t>
+          <t>AJ Barner</t>
         </is>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F249" s="3" t="n">
@@ -8468,7 +8468,7 @@
         <v>0</v>
       </c>
       <c r="H249" s="3" t="n">
-        <v>206</v>
+        <v>247</v>
       </c>
     </row>
     <row r="250">
@@ -8478,117 +8478,117 @@
         </is>
       </c>
       <c r="B250" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="C250" s="4" t="n">
+        <v>257</v>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>Kenny Pickett</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" s="3" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="n">
+        <v>317</v>
+      </c>
+      <c r="C251" s="4" t="n">
+        <v>231</v>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>Spencer Rattler</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" s="3" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="n">
+        <v>318</v>
+      </c>
+      <c r="C252" s="4" t="n">
+        <v>258</v>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>Kirk Cousins</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="F252" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G252" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" s="3" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="n">
         <v>319</v>
       </c>
-      <c r="C250" s="4" t="n">
-        <v>243</v>
-      </c>
-      <c r="D250" s="3" t="inlineStr">
+      <c r="C253" s="4" t="n">
+        <v>259</v>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
         <is>
           <t>Jalen Milroe</t>
         </is>
       </c>
-      <c r="E250" s="3" t="inlineStr">
+      <c r="E253" s="3" t="inlineStr">
         <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="F250" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G250" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H250" s="3" t="n">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="10" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B251" s="3" t="n">
-        <v>324</v>
-      </c>
-      <c r="C251" s="4" t="n">
-        <v>263</v>
-      </c>
-      <c r="D251" s="3" t="inlineStr">
-        <is>
-          <t>Will Dissly</t>
-        </is>
-      </c>
-      <c r="E251" s="3" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
-      <c r="F251" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G251" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H251" s="3" t="n">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="10" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B252" s="3" t="n">
-        <v>325</v>
-      </c>
-      <c r="C252" s="4" t="n">
-        <v>250</v>
-      </c>
-      <c r="D252" s="3" t="inlineStr">
-        <is>
-          <t>Noah Gray</t>
-        </is>
-      </c>
-      <c r="E252" s="3" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="F252" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G252" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H252" s="3" t="n">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="10" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B253" s="3" t="n">
-        <v>327</v>
-      </c>
-      <c r="C253" s="4" t="n">
-        <v>239</v>
-      </c>
-      <c r="D253" s="3" t="inlineStr">
-        <is>
-          <t>Cole Kmet</t>
-        </is>
-      </c>
-      <c r="E253" s="3" t="inlineStr">
-        <is>
-          <t>CHI</t>
-        </is>
-      </c>
       <c r="F253" s="3" t="n">
         <v>0</v>
       </c>
@@ -8596,7 +8596,7 @@
         <v>0</v>
       </c>
       <c r="H253" s="3" t="n">
-        <v>182</v>
+        <v>202</v>
       </c>
     </row>
     <row r="254">
@@ -8606,19 +8606,19 @@
         </is>
       </c>
       <c r="B254" s="3" t="n">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C254" s="4" t="n">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>Harold Fannin</t>
+          <t>Will Dissly</t>
         </is>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F254" s="3" t="n">
@@ -8628,7 +8628,7 @@
         <v>0</v>
       </c>
       <c r="H254" s="3" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="255">
@@ -8638,53 +8638,53 @@
         </is>
       </c>
       <c r="B255" s="3" t="n">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="C255" s="4" t="n">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
+          <t>Noah Gray</t>
+        </is>
+      </c>
+      <c r="E255" s="3" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="F255" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H255" s="3" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="10" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="n">
+        <v>326</v>
+      </c>
+      <c r="C256" s="4" t="n">
+        <v>271</v>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
           <t>Oronde Gadsden</t>
         </is>
       </c>
-      <c r="E255" s="3" t="inlineStr">
+      <c r="E256" s="3" t="inlineStr">
         <is>
           <t>LAC</t>
         </is>
       </c>
-      <c r="F255" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G255" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H255" s="3" t="n">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="2" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B256" s="3" t="n">
-        <v>370</v>
-      </c>
-      <c r="C256" s="4" t="n">
-        <v>254</v>
-      </c>
-      <c r="D256" s="3" t="inlineStr">
-        <is>
-          <t>Elic Ayomanor</t>
-        </is>
-      </c>
-      <c r="E256" s="3" t="inlineStr">
-        <is>
-          <t>TEN</t>
-        </is>
-      </c>
       <c r="F256" s="3" t="n">
         <v>0</v>
       </c>
@@ -8692,61 +8692,61 @@
         <v>0</v>
       </c>
       <c r="H256" s="3" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="10" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="n">
+        <v>327</v>
+      </c>
+      <c r="C257" s="4" t="n">
+        <v>256</v>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>Cole Kmet</t>
+        </is>
+      </c>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="F257" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H257" s="3" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="10" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="n">
+        <v>330</v>
+      </c>
+      <c r="C258" s="9" t="n">
         <v>194</v>
       </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B257" s="3" t="n">
-        <v>376</v>
-      </c>
-      <c r="C257" s="4" t="n">
-        <v>264</v>
-      </c>
-      <c r="D257" s="3" t="inlineStr">
-        <is>
-          <t>Chimere Dike</t>
-        </is>
-      </c>
-      <c r="E257" s="3" t="inlineStr">
-        <is>
-          <t>TEN</t>
-        </is>
-      </c>
-      <c r="F257" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G257" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H257" s="3" t="n">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="2" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B258" s="3" t="n">
-        <v>378</v>
-      </c>
-      <c r="C258" s="4" t="n">
-        <v>212</v>
-      </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>Tory Horton</t>
+          <t>Harold Fannin</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F258" s="3" t="n">
@@ -8756,7 +8756,7 @@
         <v>0</v>
       </c>
       <c r="H258" s="3" t="n">
-        <v>208</v>
+        <v>262</v>
       </c>
     </row>
     <row r="259">
@@ -8766,19 +8766,19 @@
         </is>
       </c>
       <c r="B259" s="3" t="n">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="C259" s="4" t="n">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
-          <t>Devaughn Vele</t>
+          <t>Jaylin Noel</t>
         </is>
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F259" s="3" t="n">
@@ -8788,7 +8788,7 @@
         <v>0</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>167</v>
+        <v>243</v>
       </c>
     </row>
     <row r="260">
@@ -8798,19 +8798,19 @@
         </is>
       </c>
       <c r="B260" s="3" t="n">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="C260" s="4" t="n">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>Tai Felton</t>
+          <t>Malik Washington</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F260" s="3" t="n">
@@ -8820,7 +8820,7 @@
         <v>0</v>
       </c>
       <c r="H260" s="3" t="n">
-        <v>183</v>
+        <v>162</v>
       </c>
     </row>
     <row r="261">
@@ -8830,19 +8830,19 @@
         </is>
       </c>
       <c r="B261" s="3" t="n">
-        <v>395</v>
+        <v>371</v>
       </c>
       <c r="C261" s="4" t="n">
-        <v>246</v>
+        <v>200</v>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>Marquez Valdes-Scantling</t>
+          <t>Troy Franklin</t>
         </is>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F261" s="3" t="n">
@@ -8852,7 +8852,7 @@
         <v>0</v>
       </c>
       <c r="H261" s="3" t="n">
-        <v>201</v>
+        <v>257</v>
       </c>
     </row>
     <row r="262">
@@ -8862,19 +8862,19 @@
         </is>
       </c>
       <c r="B262" s="3" t="n">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="C262" s="4" t="n">
-        <v>267</v>
+        <v>206</v>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>Jahan Dotson</t>
+          <t>Elic Ayomanor</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F262" s="3" t="n">
@@ -8884,7 +8884,231 @@
         <v>0</v>
       </c>
       <c r="H262" s="3" t="n">
-        <v>192</v>
+        <v>253</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="n">
+        <v>374</v>
+      </c>
+      <c r="C263" s="4" t="n">
+        <v>237</v>
+      </c>
+      <c r="D263" s="3" t="inlineStr">
+        <is>
+          <t>Roman Wilson</t>
+        </is>
+      </c>
+      <c r="E263" s="3" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="F263" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H263" s="3" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="n">
+        <v>375</v>
+      </c>
+      <c r="C264" s="4" t="n">
+        <v>243</v>
+      </c>
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>Kayshon Boutte</t>
+        </is>
+      </c>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="F264" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" s="3" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="n">
+        <v>379</v>
+      </c>
+      <c r="C265" s="4" t="n">
+        <v>277</v>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>Chimere Dike</t>
+        </is>
+      </c>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>TEN</t>
+        </is>
+      </c>
+      <c r="F265" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" s="3" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="n">
+        <v>380</v>
+      </c>
+      <c r="C266" s="4" t="n">
+        <v>216</v>
+      </c>
+      <c r="D266" s="3" t="inlineStr">
+        <is>
+          <t>Tory Horton</t>
+        </is>
+      </c>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="F266" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G266" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" s="3" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="n">
+        <v>387</v>
+      </c>
+      <c r="C267" s="4" t="n">
+        <v>268</v>
+      </c>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>Tai Felton</t>
+        </is>
+      </c>
+      <c r="E267" s="3" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="F267" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G267" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H267" s="3" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="n">
+        <v>396</v>
+      </c>
+      <c r="C268" s="4" t="n">
+        <v>262</v>
+      </c>
+      <c r="D268" s="3" t="inlineStr">
+        <is>
+          <t>Marquez Valdes-Scantling</t>
+        </is>
+      </c>
+      <c r="E268" s="3" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="F268" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H268" s="3" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="n">
+        <v>399</v>
+      </c>
+      <c r="C269" s="4" t="n">
+        <v>239</v>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>Olamide Zaccheaus</t>
+        </is>
+      </c>
+      <c r="E269" s="3" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="F269" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G269" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H269" s="3" t="n">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
